--- a/output/version3/test/15-10/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>851</v>
+        <v>667</v>
       </c>
       <c r="C2" t="n">
-        <v>726</v>
+        <v>652</v>
       </c>
       <c r="D2" t="n">
-        <v>774</v>
+        <v>587</v>
       </c>
       <c r="E2" t="n">
-        <v>792</v>
+        <v>598</v>
       </c>
       <c r="F2" t="n">
-        <v>687</v>
+        <v>664</v>
       </c>
       <c r="G2" t="n">
-        <v>744</v>
+        <v>627</v>
       </c>
       <c r="H2" t="n">
-        <v>660</v>
+        <v>577</v>
       </c>
       <c r="I2" t="n">
-        <v>725</v>
+        <v>591</v>
       </c>
       <c r="J2" t="n">
-        <v>807</v>
+        <v>626</v>
       </c>
       <c r="K2" t="n">
-        <v>661</v>
+        <v>579</v>
       </c>
       <c r="L2" t="n">
-        <v>742.7</v>
+        <v>616.8</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>742</v>
+        <v>521</v>
       </c>
       <c r="C3" t="n">
-        <v>822</v>
+        <v>617</v>
       </c>
       <c r="D3" t="n">
-        <v>677</v>
+        <v>631</v>
       </c>
       <c r="E3" t="n">
-        <v>701</v>
+        <v>575</v>
       </c>
       <c r="F3" t="n">
-        <v>752</v>
+        <v>600</v>
       </c>
       <c r="G3" t="n">
-        <v>650</v>
+        <v>552</v>
       </c>
       <c r="H3" t="n">
-        <v>783</v>
+        <v>567</v>
       </c>
       <c r="I3" t="n">
-        <v>895</v>
+        <v>625</v>
       </c>
       <c r="J3" t="n">
-        <v>900</v>
+        <v>580</v>
       </c>
       <c r="K3" t="n">
-        <v>820</v>
+        <v>620</v>
       </c>
       <c r="L3" t="n">
-        <v>774.2</v>
+        <v>588.8</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>734</v>
+        <v>618</v>
       </c>
       <c r="C4" t="n">
-        <v>666</v>
+        <v>630</v>
       </c>
       <c r="D4" t="n">
-        <v>705</v>
+        <v>740</v>
       </c>
       <c r="E4" t="n">
-        <v>682</v>
+        <v>759</v>
       </c>
       <c r="F4" t="n">
-        <v>750</v>
+        <v>635</v>
       </c>
       <c r="G4" t="n">
-        <v>783</v>
+        <v>662</v>
       </c>
       <c r="H4" t="n">
-        <v>767</v>
+        <v>597</v>
       </c>
       <c r="I4" t="n">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="J4" t="n">
-        <v>730</v>
+        <v>599</v>
       </c>
       <c r="K4" t="n">
-        <v>807</v>
+        <v>601</v>
       </c>
       <c r="L4" t="n">
-        <v>722.1</v>
+        <v>642.9</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>672</v>
+        <v>757</v>
       </c>
       <c r="C5" t="n">
-        <v>678</v>
+        <v>742</v>
       </c>
       <c r="D5" t="n">
-        <v>749</v>
+        <v>655</v>
       </c>
       <c r="E5" t="n">
-        <v>866</v>
+        <v>730</v>
       </c>
       <c r="F5" t="n">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="G5" t="n">
-        <v>719</v>
+        <v>637</v>
       </c>
       <c r="H5" t="n">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="I5" t="n">
-        <v>629</v>
+        <v>750</v>
       </c>
       <c r="J5" t="n">
-        <v>623</v>
+        <v>661</v>
       </c>
       <c r="K5" t="n">
-        <v>685</v>
+        <v>651</v>
       </c>
       <c r="L5" t="n">
-        <v>710.1</v>
+        <v>702.6</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>674</v>
+        <v>574</v>
       </c>
       <c r="C6" t="n">
-        <v>879</v>
+        <v>582</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>682</v>
       </c>
       <c r="E6" t="n">
-        <v>701</v>
+        <v>608</v>
       </c>
       <c r="F6" t="n">
-        <v>774</v>
+        <v>651</v>
       </c>
       <c r="G6" t="n">
-        <v>818</v>
+        <v>607</v>
       </c>
       <c r="H6" t="n">
-        <v>733</v>
+        <v>594</v>
       </c>
       <c r="I6" t="n">
-        <v>787</v>
+        <v>593</v>
       </c>
       <c r="J6" t="n">
-        <v>781</v>
+        <v>568</v>
       </c>
       <c r="K6" t="n">
-        <v>776</v>
+        <v>618</v>
       </c>
       <c r="L6" t="n">
-        <v>768.1</v>
+        <v>607.7</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>680</v>
+        <v>728</v>
       </c>
       <c r="C7" t="n">
-        <v>766</v>
+        <v>612</v>
       </c>
       <c r="D7" t="n">
-        <v>676</v>
+        <v>569</v>
       </c>
       <c r="E7" t="n">
-        <v>751</v>
+        <v>719</v>
       </c>
       <c r="F7" t="n">
-        <v>717</v>
+        <v>579</v>
       </c>
       <c r="G7" t="n">
-        <v>648</v>
+        <v>608</v>
       </c>
       <c r="H7" t="n">
-        <v>711</v>
+        <v>627</v>
       </c>
       <c r="I7" t="n">
-        <v>759</v>
+        <v>681</v>
       </c>
       <c r="J7" t="n">
-        <v>760</v>
+        <v>582</v>
       </c>
       <c r="K7" t="n">
-        <v>725</v>
+        <v>608</v>
       </c>
       <c r="L7" t="n">
-        <v>719.3</v>
+        <v>631.3</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>787</v>
+        <v>681</v>
       </c>
       <c r="C8" t="n">
-        <v>748</v>
+        <v>599</v>
       </c>
       <c r="D8" t="n">
-        <v>717</v>
+        <v>699</v>
       </c>
       <c r="E8" t="n">
-        <v>763</v>
+        <v>522</v>
       </c>
       <c r="F8" t="n">
-        <v>747</v>
+        <v>595</v>
       </c>
       <c r="G8" t="n">
-        <v>724</v>
+        <v>650</v>
       </c>
       <c r="H8" t="n">
-        <v>600</v>
+        <v>631</v>
       </c>
       <c r="I8" t="n">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="J8" t="n">
-        <v>787</v>
+        <v>641</v>
       </c>
       <c r="K8" t="n">
-        <v>858</v>
+        <v>559</v>
       </c>
       <c r="L8" t="n">
-        <v>737.4</v>
+        <v>620.8</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>811</v>
+        <v>643</v>
       </c>
       <c r="C9" t="n">
-        <v>615</v>
+        <v>593</v>
       </c>
       <c r="D9" t="n">
-        <v>707</v>
+        <v>596</v>
       </c>
       <c r="E9" t="n">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="F9" t="n">
-        <v>610</v>
+        <v>573</v>
       </c>
       <c r="G9" t="n">
-        <v>864</v>
+        <v>598</v>
       </c>
       <c r="H9" t="n">
-        <v>793</v>
+        <v>564</v>
       </c>
       <c r="I9" t="n">
-        <v>727</v>
+        <v>628</v>
       </c>
       <c r="J9" t="n">
-        <v>853</v>
+        <v>601</v>
       </c>
       <c r="K9" t="n">
-        <v>694</v>
+        <v>655</v>
       </c>
       <c r="L9" t="n">
-        <v>731.2</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>782</v>
+        <v>716</v>
       </c>
       <c r="C10" t="n">
-        <v>794</v>
+        <v>754</v>
       </c>
       <c r="D10" t="n">
-        <v>797</v>
+        <v>684</v>
       </c>
       <c r="E10" t="n">
-        <v>831</v>
+        <v>807</v>
       </c>
       <c r="F10" t="n">
-        <v>836</v>
+        <v>863</v>
       </c>
       <c r="G10" t="n">
-        <v>863</v>
+        <v>677</v>
       </c>
       <c r="H10" t="n">
-        <v>858</v>
+        <v>758</v>
       </c>
       <c r="I10" t="n">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="J10" t="n">
-        <v>843</v>
+        <v>810</v>
       </c>
       <c r="K10" t="n">
-        <v>903</v>
+        <v>753</v>
       </c>
       <c r="L10" t="n">
-        <v>830.5</v>
+        <v>758.9</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>741</v>
+        <v>633</v>
       </c>
       <c r="C11" t="n">
-        <v>673</v>
+        <v>606</v>
       </c>
       <c r="D11" t="n">
-        <v>779</v>
+        <v>574</v>
       </c>
       <c r="E11" t="n">
-        <v>636</v>
+        <v>607</v>
       </c>
       <c r="F11" t="n">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="G11" t="n">
-        <v>726</v>
+        <v>652</v>
       </c>
       <c r="H11" t="n">
-        <v>815</v>
+        <v>562</v>
       </c>
       <c r="I11" t="n">
-        <v>781</v>
+        <v>674</v>
       </c>
       <c r="J11" t="n">
-        <v>948</v>
+        <v>622</v>
       </c>
       <c r="K11" t="n">
-        <v>725</v>
+        <v>670</v>
       </c>
       <c r="L11" t="n">
-        <v>755.8</v>
+        <v>632.3</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>648</v>
+        <v>614</v>
       </c>
       <c r="C12" t="n">
-        <v>691</v>
+        <v>629</v>
       </c>
       <c r="D12" t="n">
-        <v>712</v>
+        <v>661</v>
       </c>
       <c r="E12" t="n">
-        <v>739</v>
+        <v>606</v>
       </c>
       <c r="F12" t="n">
-        <v>794</v>
+        <v>636</v>
       </c>
       <c r="G12" t="n">
-        <v>676</v>
+        <v>634</v>
       </c>
       <c r="H12" t="n">
-        <v>709</v>
+        <v>683</v>
       </c>
       <c r="I12" t="n">
-        <v>776</v>
+        <v>637</v>
       </c>
       <c r="J12" t="n">
-        <v>755</v>
+        <v>633</v>
       </c>
       <c r="K12" t="n">
-        <v>683</v>
+        <v>640</v>
       </c>
       <c r="L12" t="n">
-        <v>718.3</v>
+        <v>637.3</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>781</v>
+        <v>716</v>
       </c>
       <c r="C13" t="n">
-        <v>827</v>
+        <v>703</v>
       </c>
       <c r="D13" t="n">
-        <v>748</v>
+        <v>805</v>
       </c>
       <c r="E13" t="n">
-        <v>936</v>
+        <v>757</v>
       </c>
       <c r="F13" t="n">
-        <v>974</v>
+        <v>657</v>
       </c>
       <c r="G13" t="n">
-        <v>787</v>
+        <v>813</v>
       </c>
       <c r="H13" t="n">
-        <v>838</v>
+        <v>758</v>
       </c>
       <c r="I13" t="n">
-        <v>785</v>
+        <v>775</v>
       </c>
       <c r="J13" t="n">
-        <v>823</v>
+        <v>629</v>
       </c>
       <c r="K13" t="n">
-        <v>838</v>
+        <v>701</v>
       </c>
       <c r="L13" t="n">
-        <v>833.7</v>
+        <v>731.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>906</v>
+        <v>574</v>
       </c>
       <c r="C14" t="n">
-        <v>741</v>
+        <v>712</v>
       </c>
       <c r="D14" t="n">
-        <v>782</v>
+        <v>657</v>
       </c>
       <c r="E14" t="n">
-        <v>754</v>
+        <v>717</v>
       </c>
       <c r="F14" t="n">
-        <v>809</v>
+        <v>663</v>
       </c>
       <c r="G14" t="n">
-        <v>811</v>
+        <v>662</v>
       </c>
       <c r="H14" t="n">
-        <v>798</v>
+        <v>831</v>
       </c>
       <c r="I14" t="n">
-        <v>940</v>
+        <v>660</v>
       </c>
       <c r="J14" t="n">
-        <v>790</v>
+        <v>758</v>
       </c>
       <c r="K14" t="n">
-        <v>922</v>
+        <v>684</v>
       </c>
       <c r="L14" t="n">
-        <v>825.3</v>
+        <v>691.8</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>846</v>
+        <v>732</v>
       </c>
       <c r="C15" t="n">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="D15" t="n">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="E15" t="n">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="F15" t="n">
-        <v>640</v>
+        <v>668</v>
       </c>
       <c r="G15" t="n">
-        <v>907</v>
+        <v>794</v>
       </c>
       <c r="H15" t="n">
-        <v>865</v>
+        <v>688</v>
       </c>
       <c r="I15" t="n">
-        <v>843</v>
+        <v>610</v>
       </c>
       <c r="J15" t="n">
-        <v>815</v>
+        <v>700</v>
       </c>
       <c r="K15" t="n">
-        <v>778</v>
+        <v>721</v>
       </c>
       <c r="L15" t="n">
-        <v>789.1</v>
+        <v>708.2</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>610</v>
+        <v>708</v>
       </c>
       <c r="C16" t="n">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="D16" t="n">
-        <v>665</v>
+        <v>621</v>
       </c>
       <c r="E16" t="n">
-        <v>796</v>
+        <v>662</v>
       </c>
       <c r="F16" t="n">
-        <v>823</v>
+        <v>705</v>
       </c>
       <c r="G16" t="n">
-        <v>776</v>
+        <v>655</v>
       </c>
       <c r="H16" t="n">
-        <v>693</v>
+        <v>779</v>
       </c>
       <c r="I16" t="n">
-        <v>712</v>
+        <v>623</v>
       </c>
       <c r="J16" t="n">
-        <v>791</v>
+        <v>738</v>
       </c>
       <c r="K16" t="n">
-        <v>677</v>
+        <v>710</v>
       </c>
       <c r="L16" t="n">
-        <v>724.2</v>
+        <v>687.8</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>791</v>
+        <v>643</v>
       </c>
       <c r="C17" t="n">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="D17" t="n">
-        <v>800</v>
+        <v>632</v>
       </c>
       <c r="E17" t="n">
-        <v>840</v>
+        <v>626</v>
       </c>
       <c r="F17" t="n">
-        <v>682</v>
+        <v>603</v>
       </c>
       <c r="G17" t="n">
-        <v>859</v>
+        <v>677</v>
       </c>
       <c r="H17" t="n">
-        <v>801</v>
+        <v>602</v>
       </c>
       <c r="I17" t="n">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="J17" t="n">
-        <v>830</v>
+        <v>695</v>
       </c>
       <c r="K17" t="n">
-        <v>799</v>
+        <v>610</v>
       </c>
       <c r="L17" t="n">
-        <v>762.9</v>
+        <v>634.2</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>782</v>
+        <v>661</v>
       </c>
       <c r="C18" t="n">
-        <v>753</v>
+        <v>658</v>
       </c>
       <c r="D18" t="n">
-        <v>732</v>
+        <v>699</v>
       </c>
       <c r="E18" t="n">
-        <v>986</v>
+        <v>690</v>
       </c>
       <c r="F18" t="n">
-        <v>800</v>
+        <v>765</v>
       </c>
       <c r="G18" t="n">
-        <v>741</v>
+        <v>631</v>
       </c>
       <c r="H18" t="n">
-        <v>924</v>
+        <v>772</v>
       </c>
       <c r="I18" t="n">
-        <v>843</v>
+        <v>730</v>
       </c>
       <c r="J18" t="n">
-        <v>785</v>
+        <v>627</v>
       </c>
       <c r="K18" t="n">
-        <v>755</v>
+        <v>820</v>
       </c>
       <c r="L18" t="n">
-        <v>810.1</v>
+        <v>705.3</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>783</v>
+        <v>691</v>
       </c>
       <c r="C19" t="n">
-        <v>846</v>
+        <v>655</v>
       </c>
       <c r="D19" t="n">
-        <v>714</v>
+        <v>605</v>
       </c>
       <c r="E19" t="n">
-        <v>928</v>
+        <v>784</v>
       </c>
       <c r="F19" t="n">
-        <v>914</v>
+        <v>764</v>
       </c>
       <c r="G19" t="n">
-        <v>879</v>
+        <v>621</v>
       </c>
       <c r="H19" t="n">
-        <v>709</v>
+        <v>657</v>
       </c>
       <c r="I19" t="n">
-        <v>825</v>
+        <v>676</v>
       </c>
       <c r="J19" t="n">
-        <v>768</v>
+        <v>609</v>
       </c>
       <c r="K19" t="n">
-        <v>763</v>
+        <v>796</v>
       </c>
       <c r="L19" t="n">
-        <v>812.9</v>
+        <v>685.8</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>733</v>
+        <v>865</v>
       </c>
       <c r="C20" t="n">
-        <v>900</v>
+        <v>754</v>
       </c>
       <c r="D20" t="n">
-        <v>903</v>
+        <v>723</v>
       </c>
       <c r="E20" t="n">
-        <v>865</v>
+        <v>790</v>
       </c>
       <c r="F20" t="n">
-        <v>973</v>
+        <v>714</v>
       </c>
       <c r="G20" t="n">
-        <v>770</v>
+        <v>744</v>
       </c>
       <c r="H20" t="n">
-        <v>825</v>
+        <v>782</v>
       </c>
       <c r="I20" t="n">
-        <v>917</v>
+        <v>820</v>
       </c>
       <c r="J20" t="n">
-        <v>999</v>
+        <v>744</v>
       </c>
       <c r="K20" t="n">
-        <v>818</v>
+        <v>739</v>
       </c>
       <c r="L20" t="n">
-        <v>870.3</v>
+        <v>767.5</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>805</v>
+        <v>710</v>
       </c>
       <c r="C21" t="n">
-        <v>805</v>
+        <v>725</v>
       </c>
       <c r="D21" t="n">
-        <v>869</v>
+        <v>583</v>
       </c>
       <c r="E21" t="n">
-        <v>886</v>
+        <v>676</v>
       </c>
       <c r="F21" t="n">
-        <v>805</v>
+        <v>643</v>
       </c>
       <c r="G21" t="n">
-        <v>794</v>
+        <v>661</v>
       </c>
       <c r="H21" t="n">
-        <v>831</v>
+        <v>749</v>
       </c>
       <c r="I21" t="n">
-        <v>862</v>
+        <v>775</v>
       </c>
       <c r="J21" t="n">
-        <v>830</v>
+        <v>565</v>
       </c>
       <c r="K21" t="n">
-        <v>744</v>
+        <v>671</v>
       </c>
       <c r="L21" t="n">
-        <v>823.1</v>
+        <v>675.8</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>831</v>
+        <v>602</v>
       </c>
       <c r="C22" t="n">
-        <v>763</v>
+        <v>695</v>
       </c>
       <c r="D22" t="n">
-        <v>665</v>
+        <v>603</v>
       </c>
       <c r="E22" t="n">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="F22" t="n">
-        <v>734</v>
+        <v>703</v>
       </c>
       <c r="G22" t="n">
-        <v>799</v>
+        <v>741</v>
       </c>
       <c r="H22" t="n">
-        <v>807</v>
+        <v>653</v>
       </c>
       <c r="I22" t="n">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="J22" t="n">
-        <v>775</v>
+        <v>718</v>
       </c>
       <c r="K22" t="n">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="L22" t="n">
-        <v>747.9</v>
+        <v>681.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>811</v>
+        <v>639</v>
       </c>
       <c r="C23" t="n">
-        <v>848</v>
+        <v>783</v>
       </c>
       <c r="D23" t="n">
-        <v>753</v>
+        <v>589</v>
       </c>
       <c r="E23" t="n">
-        <v>798</v>
+        <v>566</v>
       </c>
       <c r="F23" t="n">
-        <v>759</v>
+        <v>664</v>
       </c>
       <c r="G23" t="n">
-        <v>672</v>
+        <v>633</v>
       </c>
       <c r="H23" t="n">
-        <v>796</v>
+        <v>609</v>
       </c>
       <c r="I23" t="n">
-        <v>805</v>
+        <v>703</v>
       </c>
       <c r="J23" t="n">
-        <v>818</v>
+        <v>658</v>
       </c>
       <c r="K23" t="n">
-        <v>733</v>
+        <v>665</v>
       </c>
       <c r="L23" t="n">
-        <v>779.3</v>
+        <v>650.9</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="C24" t="n">
-        <v>751</v>
+        <v>883</v>
       </c>
       <c r="D24" t="n">
-        <v>778</v>
+        <v>840</v>
       </c>
       <c r="E24" t="n">
-        <v>743</v>
+        <v>805</v>
       </c>
       <c r="F24" t="n">
-        <v>775</v>
+        <v>876</v>
       </c>
       <c r="G24" t="n">
-        <v>936</v>
+        <v>694</v>
       </c>
       <c r="H24" t="n">
-        <v>868</v>
+        <v>779</v>
       </c>
       <c r="I24" t="n">
-        <v>705</v>
+        <v>757</v>
       </c>
       <c r="J24" t="n">
-        <v>875</v>
+        <v>767</v>
       </c>
       <c r="K24" t="n">
-        <v>742</v>
+        <v>821</v>
       </c>
       <c r="L24" t="n">
-        <v>791.8</v>
+        <v>794.9</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="C25" t="n">
-        <v>747</v>
+        <v>619</v>
       </c>
       <c r="D25" t="n">
-        <v>676</v>
+        <v>652</v>
       </c>
       <c r="E25" t="n">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="F25" t="n">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="G25" t="n">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="H25" t="n">
-        <v>855</v>
+        <v>743</v>
       </c>
       <c r="I25" t="n">
-        <v>739</v>
+        <v>712</v>
       </c>
       <c r="J25" t="n">
-        <v>852</v>
+        <v>672</v>
       </c>
       <c r="K25" t="n">
-        <v>842</v>
+        <v>665</v>
       </c>
       <c r="L25" t="n">
-        <v>757.8</v>
+        <v>692.7</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>925</v>
+        <v>649</v>
       </c>
       <c r="C26" t="n">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="D26" t="n">
-        <v>700</v>
+        <v>641</v>
       </c>
       <c r="E26" t="n">
-        <v>717</v>
+        <v>597</v>
       </c>
       <c r="F26" t="n">
-        <v>634</v>
+        <v>796</v>
       </c>
       <c r="G26" t="n">
-        <v>779</v>
+        <v>592</v>
       </c>
       <c r="H26" t="n">
-        <v>824</v>
+        <v>666</v>
       </c>
       <c r="I26" t="n">
-        <v>794</v>
+        <v>647</v>
       </c>
       <c r="J26" t="n">
-        <v>667</v>
+        <v>582</v>
       </c>
       <c r="K26" t="n">
-        <v>753</v>
+        <v>638</v>
       </c>
       <c r="L26" t="n">
-        <v>762.3</v>
+        <v>662.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>691</v>
+        <v>724</v>
       </c>
       <c r="C27" t="n">
-        <v>571</v>
+        <v>664</v>
       </c>
       <c r="D27" t="n">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="E27" t="n">
-        <v>726</v>
+        <v>635</v>
       </c>
       <c r="F27" t="n">
-        <v>769</v>
+        <v>607</v>
       </c>
       <c r="G27" t="n">
-        <v>783</v>
+        <v>521</v>
       </c>
       <c r="H27" t="n">
-        <v>775</v>
+        <v>577</v>
       </c>
       <c r="I27" t="n">
-        <v>658</v>
+        <v>631</v>
       </c>
       <c r="J27" t="n">
-        <v>705</v>
+        <v>663</v>
       </c>
       <c r="K27" t="n">
-        <v>739</v>
+        <v>678</v>
       </c>
       <c r="L27" t="n">
-        <v>708.4</v>
+        <v>636.1</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>818</v>
+        <v>638</v>
       </c>
       <c r="C28" t="n">
-        <v>677</v>
+        <v>628</v>
       </c>
       <c r="D28" t="n">
-        <v>680</v>
+        <v>622</v>
       </c>
       <c r="E28" t="n">
-        <v>637</v>
+        <v>622</v>
       </c>
       <c r="F28" t="n">
-        <v>814</v>
+        <v>628</v>
       </c>
       <c r="G28" t="n">
-        <v>745</v>
+        <v>627</v>
       </c>
       <c r="H28" t="n">
-        <v>934</v>
+        <v>615</v>
       </c>
       <c r="I28" t="n">
-        <v>754</v>
+        <v>604</v>
       </c>
       <c r="J28" t="n">
-        <v>741</v>
+        <v>588</v>
       </c>
       <c r="K28" t="n">
-        <v>827</v>
+        <v>655</v>
       </c>
       <c r="L28" t="n">
-        <v>762.7</v>
+        <v>622.7</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>754</v>
+        <v>694</v>
       </c>
       <c r="C29" t="n">
-        <v>814</v>
+        <v>671</v>
       </c>
       <c r="D29" t="n">
-        <v>781</v>
+        <v>580</v>
       </c>
       <c r="E29" t="n">
-        <v>770</v>
+        <v>730</v>
       </c>
       <c r="F29" t="n">
-        <v>734</v>
+        <v>705</v>
       </c>
       <c r="G29" t="n">
-        <v>727</v>
+        <v>703</v>
       </c>
       <c r="H29" t="n">
-        <v>695</v>
+        <v>631</v>
       </c>
       <c r="I29" t="n">
-        <v>794</v>
+        <v>627</v>
       </c>
       <c r="J29" t="n">
-        <v>761</v>
+        <v>538</v>
       </c>
       <c r="K29" t="n">
-        <v>778</v>
+        <v>619</v>
       </c>
       <c r="L29" t="n">
-        <v>760.8</v>
+        <v>649.8</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>906</v>
+        <v>635</v>
       </c>
       <c r="C30" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="D30" t="n">
-        <v>811</v>
+        <v>668</v>
       </c>
       <c r="E30" t="n">
-        <v>723</v>
+        <v>657</v>
       </c>
       <c r="F30" t="n">
-        <v>745</v>
+        <v>643</v>
       </c>
       <c r="G30" t="n">
-        <v>708</v>
+        <v>681</v>
       </c>
       <c r="H30" t="n">
+        <v>652</v>
+      </c>
+      <c r="I30" t="n">
         <v>651</v>
       </c>
-      <c r="I30" t="n">
-        <v>690</v>
-      </c>
       <c r="J30" t="n">
-        <v>762</v>
+        <v>595</v>
       </c>
       <c r="K30" t="n">
-        <v>775</v>
+        <v>666</v>
       </c>
       <c r="L30" t="n">
-        <v>747.8</v>
+        <v>654.7</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>968</v>
+        <v>739</v>
       </c>
       <c r="C31" t="n">
-        <v>762</v>
+        <v>796</v>
       </c>
       <c r="D31" t="n">
+        <v>719</v>
+      </c>
+      <c r="E31" t="n">
+        <v>685</v>
+      </c>
+      <c r="F31" t="n">
+        <v>717</v>
+      </c>
+      <c r="G31" t="n">
+        <v>758</v>
+      </c>
+      <c r="H31" t="n">
+        <v>747</v>
+      </c>
+      <c r="I31" t="n">
+        <v>861</v>
+      </c>
+      <c r="J31" t="n">
+        <v>870</v>
+      </c>
+      <c r="K31" t="n">
         <v>741</v>
       </c>
-      <c r="E31" t="n">
-        <v>782</v>
-      </c>
-      <c r="F31" t="n">
-        <v>828</v>
-      </c>
-      <c r="G31" t="n">
-        <v>818</v>
-      </c>
-      <c r="H31" t="n">
-        <v>833</v>
-      </c>
-      <c r="I31" t="n">
-        <v>768</v>
-      </c>
-      <c r="J31" t="n">
-        <v>921</v>
-      </c>
-      <c r="K31" t="n">
-        <v>921</v>
-      </c>
       <c r="L31" t="n">
-        <v>834.2</v>
+        <v>763.3</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>895</v>
+        <v>746</v>
       </c>
       <c r="C32" t="n">
-        <v>856</v>
+        <v>732</v>
       </c>
       <c r="D32" t="n">
-        <v>962</v>
+        <v>698</v>
       </c>
       <c r="E32" t="n">
-        <v>918</v>
+        <v>629</v>
       </c>
       <c r="F32" t="n">
-        <v>737</v>
+        <v>677</v>
       </c>
       <c r="G32" t="n">
-        <v>814</v>
+        <v>712</v>
       </c>
       <c r="H32" t="n">
-        <v>742</v>
+        <v>628</v>
       </c>
       <c r="I32" t="n">
-        <v>911</v>
+        <v>698</v>
       </c>
       <c r="J32" t="n">
-        <v>806</v>
+        <v>671</v>
       </c>
       <c r="K32" t="n">
-        <v>714</v>
+        <v>671</v>
       </c>
       <c r="L32" t="n">
-        <v>835.5</v>
+        <v>686.2</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>887</v>
+        <v>723</v>
       </c>
       <c r="C33" t="n">
-        <v>768</v>
+        <v>827</v>
       </c>
       <c r="D33" t="n">
-        <v>830</v>
+        <v>608</v>
       </c>
       <c r="E33" t="n">
-        <v>776</v>
+        <v>808</v>
       </c>
       <c r="F33" t="n">
-        <v>768</v>
+        <v>668</v>
       </c>
       <c r="G33" t="n">
-        <v>901</v>
+        <v>697</v>
       </c>
       <c r="H33" t="n">
-        <v>878</v>
+        <v>793</v>
       </c>
       <c r="I33" t="n">
-        <v>770</v>
+        <v>704</v>
       </c>
       <c r="J33" t="n">
-        <v>803</v>
+        <v>726</v>
       </c>
       <c r="K33" t="n">
-        <v>925</v>
+        <v>638</v>
       </c>
       <c r="L33" t="n">
-        <v>830.6</v>
+        <v>719.2</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>690</v>
+        <v>596</v>
       </c>
       <c r="C34" t="n">
-        <v>751</v>
+        <v>620</v>
       </c>
       <c r="D34" t="n">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="E34" t="n">
-        <v>667</v>
+        <v>630</v>
       </c>
       <c r="F34" t="n">
-        <v>704</v>
+        <v>589</v>
       </c>
       <c r="G34" t="n">
-        <v>684</v>
+        <v>577</v>
       </c>
       <c r="H34" t="n">
-        <v>722</v>
+        <v>651</v>
       </c>
       <c r="I34" t="n">
-        <v>754</v>
+        <v>646</v>
       </c>
       <c r="J34" t="n">
-        <v>678</v>
+        <v>719</v>
       </c>
       <c r="K34" t="n">
-        <v>766</v>
+        <v>735</v>
       </c>
       <c r="L34" t="n">
-        <v>707.2</v>
+        <v>641.2</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>830</v>
+        <v>694</v>
       </c>
       <c r="C35" t="n">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="D35" t="n">
-        <v>743</v>
+        <v>666</v>
       </c>
       <c r="E35" t="n">
-        <v>707</v>
+        <v>677</v>
       </c>
       <c r="F35" t="n">
         <v>682</v>
       </c>
       <c r="G35" t="n">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="H35" t="n">
-        <v>721</v>
+        <v>657</v>
       </c>
       <c r="I35" t="n">
-        <v>678</v>
+        <v>609</v>
       </c>
       <c r="J35" t="n">
-        <v>760</v>
+        <v>605</v>
       </c>
       <c r="K35" t="n">
-        <v>689</v>
+        <v>631</v>
       </c>
       <c r="L35" t="n">
-        <v>717.6</v>
+        <v>655.7</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>777</v>
+        <v>728</v>
       </c>
       <c r="C36" t="n">
-        <v>774</v>
+        <v>652</v>
       </c>
       <c r="D36" t="n">
-        <v>894</v>
+        <v>611</v>
       </c>
       <c r="E36" t="n">
-        <v>828</v>
+        <v>694</v>
       </c>
       <c r="F36" t="n">
-        <v>753</v>
+        <v>742</v>
       </c>
       <c r="G36" t="n">
-        <v>809</v>
+        <v>660</v>
       </c>
       <c r="H36" t="n">
-        <v>835</v>
+        <v>667</v>
       </c>
       <c r="I36" t="n">
-        <v>852</v>
+        <v>687</v>
       </c>
       <c r="J36" t="n">
-        <v>810</v>
+        <v>749</v>
       </c>
       <c r="K36" t="n">
-        <v>798</v>
+        <v>756</v>
       </c>
       <c r="L36" t="n">
-        <v>813</v>
+        <v>694.6</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>815</v>
+        <v>719</v>
       </c>
       <c r="C37" t="n">
-        <v>659</v>
+        <v>723</v>
       </c>
       <c r="D37" t="n">
-        <v>632</v>
+        <v>702</v>
       </c>
       <c r="E37" t="n">
-        <v>714</v>
+        <v>695</v>
       </c>
       <c r="F37" t="n">
-        <v>699</v>
+        <v>816</v>
       </c>
       <c r="G37" t="n">
-        <v>870</v>
+        <v>766</v>
       </c>
       <c r="H37" t="n">
-        <v>721</v>
+        <v>691</v>
       </c>
       <c r="I37" t="n">
-        <v>811</v>
+        <v>845</v>
       </c>
       <c r="J37" t="n">
-        <v>691</v>
+        <v>805</v>
       </c>
       <c r="K37" t="n">
-        <v>908</v>
+        <v>678</v>
       </c>
       <c r="L37" t="n">
-        <v>752</v>
+        <v>744</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>805</v>
+        <v>646</v>
       </c>
       <c r="C38" t="n">
-        <v>889</v>
+        <v>644</v>
       </c>
       <c r="D38" t="n">
-        <v>738</v>
+        <v>629</v>
       </c>
       <c r="E38" t="n">
-        <v>786</v>
+        <v>648</v>
       </c>
       <c r="F38" t="n">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="G38" t="n">
-        <v>734</v>
+        <v>679</v>
       </c>
       <c r="H38" t="n">
-        <v>726</v>
+        <v>649</v>
       </c>
       <c r="I38" t="n">
-        <v>825</v>
+        <v>636</v>
       </c>
       <c r="J38" t="n">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="K38" t="n">
-        <v>847</v>
+        <v>631</v>
       </c>
       <c r="L38" t="n">
-        <v>777.7</v>
+        <v>658.2</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>752</v>
+        <v>653</v>
       </c>
       <c r="C39" t="n">
-        <v>616</v>
+        <v>578</v>
       </c>
       <c r="D39" t="n">
-        <v>846</v>
+        <v>613</v>
       </c>
       <c r="E39" t="n">
-        <v>768</v>
+        <v>573</v>
       </c>
       <c r="F39" t="n">
-        <v>660</v>
+        <v>650</v>
       </c>
       <c r="G39" t="n">
-        <v>604</v>
+        <v>696</v>
       </c>
       <c r="H39" t="n">
-        <v>589</v>
+        <v>650</v>
       </c>
       <c r="I39" t="n">
-        <v>792</v>
+        <v>548</v>
       </c>
       <c r="J39" t="n">
-        <v>691</v>
+        <v>614</v>
       </c>
       <c r="K39" t="n">
-        <v>716</v>
+        <v>577</v>
       </c>
       <c r="L39" t="n">
-        <v>703.4</v>
+        <v>615.2</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>743</v>
+        <v>815</v>
       </c>
       <c r="C40" t="n">
-        <v>721</v>
+        <v>777</v>
       </c>
       <c r="D40" t="n">
-        <v>726</v>
+        <v>630</v>
       </c>
       <c r="E40" t="n">
-        <v>819</v>
+        <v>683</v>
       </c>
       <c r="F40" t="n">
-        <v>758</v>
+        <v>635</v>
       </c>
       <c r="G40" t="n">
-        <v>788</v>
+        <v>766</v>
       </c>
       <c r="H40" t="n">
-        <v>836</v>
+        <v>752</v>
       </c>
       <c r="I40" t="n">
-        <v>839</v>
+        <v>757</v>
       </c>
       <c r="J40" t="n">
-        <v>796</v>
+        <v>725</v>
       </c>
       <c r="K40" t="n">
-        <v>649</v>
+        <v>671</v>
       </c>
       <c r="L40" t="n">
-        <v>767.5</v>
+        <v>721.1</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>713</v>
+        <v>670</v>
       </c>
       <c r="C41" t="n">
-        <v>788</v>
+        <v>681</v>
       </c>
       <c r="D41" t="n">
-        <v>737</v>
+        <v>662</v>
       </c>
       <c r="E41" t="n">
-        <v>759</v>
+        <v>581</v>
       </c>
       <c r="F41" t="n">
-        <v>795</v>
+        <v>691</v>
       </c>
       <c r="G41" t="n">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H41" t="n">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="I41" t="n">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="J41" t="n">
-        <v>738</v>
+        <v>611</v>
       </c>
       <c r="K41" t="n">
-        <v>802</v>
+        <v>689</v>
       </c>
       <c r="L41" t="n">
-        <v>742.9</v>
+        <v>665.6</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>768</v>
+        <v>638</v>
       </c>
       <c r="C42" t="n">
-        <v>731</v>
+        <v>625</v>
       </c>
       <c r="D42" t="n">
-        <v>787</v>
+        <v>646</v>
       </c>
       <c r="E42" t="n">
-        <v>715</v>
+        <v>642</v>
       </c>
       <c r="F42" t="n">
-        <v>881</v>
+        <v>641</v>
       </c>
       <c r="G42" t="n">
-        <v>724</v>
+        <v>688</v>
       </c>
       <c r="H42" t="n">
-        <v>758</v>
+        <v>623</v>
       </c>
       <c r="I42" t="n">
-        <v>862</v>
+        <v>648</v>
       </c>
       <c r="J42" t="n">
-        <v>811</v>
+        <v>763</v>
       </c>
       <c r="K42" t="n">
-        <v>905</v>
+        <v>683</v>
       </c>
       <c r="L42" t="n">
-        <v>794.2</v>
+        <v>659.7</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>779</v>
+        <v>758</v>
       </c>
       <c r="C43" t="n">
-        <v>797</v>
+        <v>651</v>
       </c>
       <c r="D43" t="n">
-        <v>734</v>
+        <v>597</v>
       </c>
       <c r="E43" t="n">
-        <v>806</v>
+        <v>737</v>
       </c>
       <c r="F43" t="n">
-        <v>840</v>
+        <v>739</v>
       </c>
       <c r="G43" t="n">
-        <v>857</v>
+        <v>819</v>
       </c>
       <c r="H43" t="n">
-        <v>795</v>
+        <v>571</v>
       </c>
       <c r="I43" t="n">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="J43" t="n">
-        <v>913</v>
+        <v>636</v>
       </c>
       <c r="K43" t="n">
-        <v>813</v>
+        <v>725</v>
       </c>
       <c r="L43" t="n">
-        <v>809</v>
+        <v>697.9</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>921</v>
+        <v>585</v>
       </c>
       <c r="C44" t="n">
-        <v>811</v>
+        <v>584</v>
       </c>
       <c r="D44" t="n">
-        <v>874</v>
+        <v>590</v>
       </c>
       <c r="E44" t="n">
-        <v>735</v>
+        <v>644</v>
       </c>
       <c r="F44" t="n">
-        <v>838</v>
+        <v>632</v>
       </c>
       <c r="G44" t="n">
-        <v>860</v>
+        <v>691</v>
       </c>
       <c r="H44" t="n">
-        <v>858</v>
+        <v>615</v>
       </c>
       <c r="I44" t="n">
-        <v>691</v>
+        <v>571</v>
       </c>
       <c r="J44" t="n">
-        <v>787</v>
+        <v>701</v>
       </c>
       <c r="K44" t="n">
-        <v>715</v>
+        <v>677</v>
       </c>
       <c r="L44" t="n">
-        <v>809</v>
+        <v>629</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>902</v>
+        <v>753</v>
       </c>
       <c r="C45" t="n">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="D45" t="n">
-        <v>718</v>
+        <v>697</v>
       </c>
       <c r="E45" t="n">
-        <v>744</v>
+        <v>786</v>
       </c>
       <c r="F45" t="n">
-        <v>762</v>
+        <v>702</v>
       </c>
       <c r="G45" t="n">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="H45" t="n">
-        <v>790</v>
+        <v>726</v>
       </c>
       <c r="I45" t="n">
-        <v>757</v>
+        <v>743</v>
       </c>
       <c r="J45" t="n">
-        <v>717</v>
+        <v>748</v>
       </c>
       <c r="K45" t="n">
-        <v>696</v>
+        <v>651</v>
       </c>
       <c r="L45" t="n">
-        <v>768.2</v>
+        <v>741.5</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C46" t="n">
-        <v>808</v>
+        <v>740</v>
       </c>
       <c r="D46" t="n">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="E46" t="n">
-        <v>705</v>
+        <v>617</v>
       </c>
       <c r="F46" t="n">
-        <v>810</v>
+        <v>742</v>
       </c>
       <c r="G46" t="n">
-        <v>772</v>
+        <v>672</v>
       </c>
       <c r="H46" t="n">
-        <v>710</v>
+        <v>587</v>
       </c>
       <c r="I46" t="n">
-        <v>886</v>
+        <v>733</v>
       </c>
       <c r="J46" t="n">
-        <v>751</v>
+        <v>713</v>
       </c>
       <c r="K46" t="n">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="L46" t="n">
-        <v>757.1</v>
+        <v>696.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>729</v>
+        <v>656</v>
       </c>
       <c r="C47" t="n">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="D47" t="n">
-        <v>594</v>
+        <v>755</v>
       </c>
       <c r="E47" t="n">
-        <v>730</v>
+        <v>637</v>
       </c>
       <c r="F47" t="n">
-        <v>729</v>
+        <v>672</v>
       </c>
       <c r="G47" t="n">
-        <v>733</v>
+        <v>580</v>
       </c>
       <c r="H47" t="n">
-        <v>737</v>
+        <v>636</v>
       </c>
       <c r="I47" t="n">
-        <v>870</v>
+        <v>574</v>
       </c>
       <c r="J47" t="n">
-        <v>869</v>
+        <v>590</v>
       </c>
       <c r="K47" t="n">
-        <v>682</v>
+        <v>674</v>
       </c>
       <c r="L47" t="n">
-        <v>740.4</v>
+        <v>652.2</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>849</v>
+        <v>820</v>
       </c>
       <c r="C48" t="n">
-        <v>817</v>
+        <v>710</v>
       </c>
       <c r="D48" t="n">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="E48" t="n">
-        <v>898</v>
+        <v>844</v>
       </c>
       <c r="F48" t="n">
-        <v>886</v>
+        <v>751</v>
       </c>
       <c r="G48" t="n">
-        <v>803</v>
+        <v>770</v>
       </c>
       <c r="H48" t="n">
-        <v>977</v>
+        <v>728</v>
       </c>
       <c r="I48" t="n">
-        <v>931</v>
+        <v>729</v>
       </c>
       <c r="J48" t="n">
-        <v>753</v>
+        <v>692</v>
       </c>
       <c r="K48" t="n">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="L48" t="n">
-        <v>839.4</v>
+        <v>752.4</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>954</v>
+        <v>796</v>
       </c>
       <c r="C49" t="n">
-        <v>731</v>
+        <v>775</v>
       </c>
       <c r="D49" t="n">
-        <v>777</v>
+        <v>800</v>
       </c>
       <c r="E49" t="n">
-        <v>705</v>
+        <v>874</v>
       </c>
       <c r="F49" t="n">
-        <v>784</v>
+        <v>853</v>
       </c>
       <c r="G49" t="n">
-        <v>812</v>
+        <v>758</v>
       </c>
       <c r="H49" t="n">
-        <v>960</v>
+        <v>884</v>
       </c>
       <c r="I49" t="n">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="J49" t="n">
-        <v>906</v>
+        <v>695</v>
       </c>
       <c r="K49" t="n">
-        <v>752</v>
+        <v>769</v>
       </c>
       <c r="L49" t="n">
-        <v>810</v>
+        <v>791.9</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>749</v>
+        <v>706</v>
       </c>
       <c r="C50" t="n">
-        <v>776</v>
+        <v>688</v>
       </c>
       <c r="D50" t="n">
-        <v>724</v>
+        <v>584</v>
       </c>
       <c r="E50" t="n">
-        <v>744</v>
+        <v>729</v>
       </c>
       <c r="F50" t="n">
-        <v>947</v>
+        <v>736</v>
       </c>
       <c r="G50" t="n">
-        <v>798</v>
+        <v>688</v>
       </c>
       <c r="H50" t="n">
-        <v>868</v>
+        <v>655</v>
       </c>
       <c r="I50" t="n">
-        <v>719</v>
+        <v>694</v>
       </c>
       <c r="J50" t="n">
-        <v>849</v>
+        <v>734</v>
       </c>
       <c r="K50" t="n">
-        <v>884</v>
+        <v>777</v>
       </c>
       <c r="L50" t="n">
-        <v>805.8</v>
+        <v>699.1</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>749</v>
+        <v>684</v>
       </c>
       <c r="C51" t="n">
-        <v>796</v>
+        <v>716</v>
       </c>
       <c r="D51" t="n">
-        <v>825</v>
+        <v>687</v>
       </c>
       <c r="E51" t="n">
-        <v>789</v>
+        <v>765</v>
       </c>
       <c r="F51" t="n">
-        <v>840</v>
+        <v>695</v>
       </c>
       <c r="G51" t="n">
-        <v>822</v>
+        <v>705</v>
       </c>
       <c r="H51" t="n">
-        <v>822</v>
+        <v>737</v>
       </c>
       <c r="I51" t="n">
-        <v>860</v>
+        <v>777</v>
       </c>
       <c r="J51" t="n">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="K51" t="n">
-        <v>685</v>
+        <v>669</v>
       </c>
       <c r="L51" t="n">
-        <v>794.5</v>
+        <v>720.4</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>788.1799999999999</v>
+        <v>687.36</v>
       </c>
       <c r="C52" t="n">
-        <v>754.3200000000001</v>
+        <v>688.5</v>
       </c>
       <c r="D52" t="n">
-        <v>749.74</v>
+        <v>659.8</v>
       </c>
       <c r="E52" t="n">
-        <v>766.9</v>
+        <v>681.62</v>
       </c>
       <c r="F52" t="n">
-        <v>773.0599999999999</v>
+        <v>689.6</v>
       </c>
       <c r="G52" t="n">
-        <v>776.28</v>
+        <v>679.0599999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>785.28</v>
+        <v>676.02</v>
       </c>
       <c r="I52" t="n">
-        <v>777.72</v>
+        <v>682.88</v>
       </c>
       <c r="J52" t="n">
-        <v>794.28</v>
+        <v>672.8</v>
       </c>
       <c r="K52" t="n">
-        <v>772.1</v>
+        <v>679.36</v>
       </c>
       <c r="L52" t="n">
-        <v>773.7860000000001</v>
+        <v>679.7</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>5.056485652923584</v>
+        <v>4.251630306243896</v>
       </c>
       <c r="C2" t="n">
-        <v>4.460949659347534</v>
+        <v>4.559806108474731</v>
       </c>
       <c r="D2" t="n">
-        <v>4.858012437820435</v>
+        <v>4.166857004165649</v>
       </c>
       <c r="E2" t="n">
-        <v>4.326006412506104</v>
+        <v>4.037203788757324</v>
       </c>
       <c r="F2" t="n">
-        <v>4.240492105484009</v>
+        <v>4.764259576797485</v>
       </c>
       <c r="G2" t="n">
-        <v>4.304584503173828</v>
+        <v>4.08607292175293</v>
       </c>
       <c r="H2" t="n">
-        <v>4.054551839828491</v>
+        <v>4.185806751251221</v>
       </c>
       <c r="I2" t="n">
-        <v>4.271986246109009</v>
+        <v>4.010275363922119</v>
       </c>
       <c r="J2" t="n">
-        <v>5.22881817817688</v>
+        <v>4.349368810653687</v>
       </c>
       <c r="K2" t="n">
-        <v>4.747115135192871</v>
+        <v>4.201764106750488</v>
       </c>
       <c r="L2" t="n">
-        <v>4.554900217056274</v>
+        <v>4.261304473876953</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>5.114888429641724</v>
+        <v>4.494979381561279</v>
       </c>
       <c r="C3" t="n">
-        <v>5.07667064666748</v>
+        <v>4.612665414810181</v>
       </c>
       <c r="D3" t="n">
-        <v>4.786894083023071</v>
+        <v>4.441123485565186</v>
       </c>
       <c r="E3" t="n">
-        <v>5.167195320129395</v>
+        <v>4.288531303405762</v>
       </c>
       <c r="F3" t="n">
-        <v>4.763428688049316</v>
+        <v>4.669512510299683</v>
       </c>
       <c r="G3" t="n">
-        <v>4.443463325500488</v>
+        <v>4.553822040557861</v>
       </c>
       <c r="H3" t="n">
-        <v>4.44477391242981</v>
+        <v>4.428158521652222</v>
       </c>
       <c r="I3" t="n">
-        <v>4.952696800231934</v>
+        <v>4.614659309387207</v>
       </c>
       <c r="J3" t="n">
-        <v>5.552874803543091</v>
+        <v>4.501960277557373</v>
       </c>
       <c r="K3" t="n">
-        <v>5.471729278564453</v>
+        <v>4.59171986579895</v>
       </c>
       <c r="L3" t="n">
-        <v>4.977461528778076</v>
+        <v>4.51971321105957</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>3.770604848861694</v>
+        <v>3.678163290023804</v>
       </c>
       <c r="C4" t="n">
-        <v>4.063966274261475</v>
+        <v>3.847710371017456</v>
       </c>
       <c r="D4" t="n">
-        <v>3.550727844238281</v>
+        <v>4.963725805282593</v>
       </c>
       <c r="E4" t="n">
-        <v>3.687972784042358</v>
+        <v>4.422174453735352</v>
       </c>
       <c r="F4" t="n">
-        <v>3.470920085906982</v>
+        <v>3.759944915771484</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0906982421875</v>
+        <v>3.914531707763672</v>
       </c>
       <c r="H4" t="n">
-        <v>3.951301336288452</v>
+        <v>3.747977018356323</v>
       </c>
       <c r="I4" t="n">
-        <v>3.94091796875</v>
+        <v>3.745983123779297</v>
       </c>
       <c r="J4" t="n">
-        <v>4.539698600769043</v>
+        <v>4.082083702087402</v>
       </c>
       <c r="K4" t="n">
-        <v>4.504362821578979</v>
+        <v>3.943454265594482</v>
       </c>
       <c r="L4" t="n">
-        <v>3.957117080688477</v>
+        <v>4.010574865341186</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.054939746856689</v>
+        <v>4.206750154495239</v>
       </c>
       <c r="C5" t="n">
-        <v>4.456758499145508</v>
+        <v>4.548835039138794</v>
       </c>
       <c r="D5" t="n">
-        <v>4.211245059967041</v>
+        <v>4.440127372741699</v>
       </c>
       <c r="E5" t="n">
-        <v>3.938488245010376</v>
+        <v>4.360338687896729</v>
       </c>
       <c r="F5" t="n">
-        <v>3.906147480010986</v>
+        <v>4.252627611160278</v>
       </c>
       <c r="G5" t="n">
-        <v>3.964374542236328</v>
+        <v>3.880623340606689</v>
       </c>
       <c r="H5" t="n">
-        <v>3.885754585266113</v>
+        <v>4.208745002746582</v>
       </c>
       <c r="I5" t="n">
-        <v>4.215547800064087</v>
+        <v>4.278557777404785</v>
       </c>
       <c r="J5" t="n">
-        <v>3.769867420196533</v>
+        <v>4.019251585006714</v>
       </c>
       <c r="K5" t="n">
-        <v>3.959797859191895</v>
+        <v>3.964398145675659</v>
       </c>
       <c r="L5" t="n">
-        <v>4.036292123794555</v>
+        <v>4.216025471687317</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>4.286137342453003</v>
+        <v>4.105021715164185</v>
       </c>
       <c r="C6" t="n">
-        <v>5.40388298034668</v>
+        <v>3.941459655761719</v>
       </c>
       <c r="D6" t="n">
-        <v>4.236097097396851</v>
+        <v>4.161871194839478</v>
       </c>
       <c r="E6" t="n">
-        <v>4.378705501556396</v>
+        <v>4.271577119827271</v>
       </c>
       <c r="F6" t="n">
-        <v>4.649605989456177</v>
+        <v>4.117987632751465</v>
       </c>
       <c r="G6" t="n">
-        <v>4.669036865234375</v>
+        <v>4.311470031738281</v>
       </c>
       <c r="H6" t="n">
-        <v>4.230468988418579</v>
+        <v>3.980355739593506</v>
       </c>
       <c r="I6" t="n">
-        <v>5.033799171447754</v>
+        <v>4.084077835083008</v>
       </c>
       <c r="J6" t="n">
-        <v>4.326215267181396</v>
+        <v>4.209742546081543</v>
       </c>
       <c r="K6" t="n">
-        <v>4.909999132156372</v>
+        <v>4.021246194839478</v>
       </c>
       <c r="L6" t="n">
-        <v>4.612394833564759</v>
+        <v>4.120480966567993</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>3.799082517623901</v>
+        <v>4.436137676239014</v>
       </c>
       <c r="C7" t="n">
-        <v>3.736820697784424</v>
+        <v>3.885608673095703</v>
       </c>
       <c r="D7" t="n">
-        <v>3.740684747695923</v>
+        <v>3.815795660018921</v>
       </c>
       <c r="E7" t="n">
-        <v>4.169310092926025</v>
+        <v>4.823102235794067</v>
       </c>
       <c r="F7" t="n">
-        <v>4.025783061981201</v>
+        <v>3.952430725097656</v>
       </c>
       <c r="G7" t="n">
-        <v>4.268909454345703</v>
+        <v>4.00528883934021</v>
       </c>
       <c r="H7" t="n">
-        <v>3.867058753967285</v>
+        <v>3.884612083435059</v>
       </c>
       <c r="I7" t="n">
-        <v>4.410894632339478</v>
+        <v>5.163192272186279</v>
       </c>
       <c r="J7" t="n">
-        <v>4.006356954574585</v>
+        <v>3.971379280090332</v>
       </c>
       <c r="K7" t="n">
-        <v>3.879829168319702</v>
+        <v>3.947443246841431</v>
       </c>
       <c r="L7" t="n">
-        <v>3.990473008155823</v>
+        <v>4.188499069213867</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.964225769042969</v>
+        <v>5.104349613189697</v>
       </c>
       <c r="C8" t="n">
-        <v>4.44722056388855</v>
+        <v>4.151896953582764</v>
       </c>
       <c r="D8" t="n">
-        <v>4.105343103408813</v>
+        <v>4.260606527328491</v>
       </c>
       <c r="E8" t="n">
-        <v>4.427089691162109</v>
+        <v>4.157880783081055</v>
       </c>
       <c r="F8" t="n">
-        <v>4.602271795272827</v>
+        <v>4.063134431838989</v>
       </c>
       <c r="G8" t="n">
-        <v>4.196818113327026</v>
+        <v>4.439128875732422</v>
       </c>
       <c r="H8" t="n">
-        <v>4.083609104156494</v>
+        <v>4.297508239746094</v>
       </c>
       <c r="I8" t="n">
-        <v>4.035814046859741</v>
+        <v>4.246643543243408</v>
       </c>
       <c r="J8" t="n">
-        <v>5.307690620422363</v>
+        <v>4.424168586730957</v>
       </c>
       <c r="K8" t="n">
-        <v>5.240257501602173</v>
+        <v>4.300499677658081</v>
       </c>
       <c r="L8" t="n">
-        <v>4.541034030914306</v>
+        <v>4.344581723213196</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>4.508402585983276</v>
+        <v>3.586409091949463</v>
       </c>
       <c r="C9" t="n">
-        <v>3.377605199813843</v>
+        <v>3.904558897018433</v>
       </c>
       <c r="D9" t="n">
-        <v>3.419759035110474</v>
+        <v>3.810808897018433</v>
       </c>
       <c r="E9" t="n">
-        <v>3.556183815002441</v>
+        <v>3.632286548614502</v>
       </c>
       <c r="F9" t="n">
-        <v>3.680766105651855</v>
+        <v>3.796846389770508</v>
       </c>
       <c r="G9" t="n">
-        <v>4.278463840484619</v>
+        <v>3.652233123779297</v>
       </c>
       <c r="H9" t="n">
-        <v>4.316630363464355</v>
+        <v>3.645251989364624</v>
       </c>
       <c r="I9" t="n">
-        <v>3.875592708587646</v>
+        <v>3.690131187438965</v>
       </c>
       <c r="J9" t="n">
-        <v>4.542533159255981</v>
+        <v>3.653230428695679</v>
       </c>
       <c r="K9" t="n">
-        <v>3.54048228263855</v>
+        <v>3.818787813186646</v>
       </c>
       <c r="L9" t="n">
-        <v>3.909641909599304</v>
+        <v>3.719054436683655</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.299256563186646</v>
+        <v>5.313790559768677</v>
       </c>
       <c r="C10" t="n">
-        <v>5.314307689666748</v>
+        <v>5.086397647857666</v>
       </c>
       <c r="D10" t="n">
-        <v>5.09894323348999</v>
+        <v>5.019575595855713</v>
       </c>
       <c r="E10" t="n">
-        <v>5.874228954315186</v>
+        <v>5.843373537063599</v>
       </c>
       <c r="F10" t="n">
-        <v>5.274832487106323</v>
+        <v>6.27122974395752</v>
       </c>
       <c r="G10" t="n">
-        <v>5.974476099014282</v>
+        <v>5.17516016960144</v>
       </c>
       <c r="H10" t="n">
-        <v>4.740886688232422</v>
+        <v>5.301822423934937</v>
       </c>
       <c r="I10" t="n">
-        <v>4.921443462371826</v>
+        <v>5.793506145477295</v>
       </c>
       <c r="J10" t="n">
-        <v>4.793621301651001</v>
+        <v>4.993646144866943</v>
       </c>
       <c r="K10" t="n">
-        <v>5.881676197052002</v>
+        <v>5.166184663772583</v>
       </c>
       <c r="L10" t="n">
-        <v>5.317367267608643</v>
+        <v>5.396468663215638</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.506407022476196</v>
+        <v>4.795176982879639</v>
       </c>
       <c r="C11" t="n">
-        <v>4.833147287368774</v>
+        <v>4.734893798828125</v>
       </c>
       <c r="D11" t="n">
-        <v>5.123383045196533</v>
+        <v>5.863113164901733</v>
       </c>
       <c r="E11" t="n">
-        <v>4.444585800170898</v>
+        <v>5.158916711807251</v>
       </c>
       <c r="F11" t="n">
-        <v>4.744400978088379</v>
+        <v>5.150838851928711</v>
       </c>
       <c r="G11" t="n">
-        <v>4.600935459136963</v>
+        <v>4.996876001358032</v>
       </c>
       <c r="H11" t="n">
-        <v>4.86245584487915</v>
+        <v>4.164861679077148</v>
       </c>
       <c r="I11" t="n">
-        <v>4.858997583389282</v>
+        <v>4.934803485870361</v>
       </c>
       <c r="J11" t="n">
-        <v>5.203685283660889</v>
+        <v>4.306864500045776</v>
       </c>
       <c r="K11" t="n">
-        <v>5.033157110214233</v>
+        <v>4.440126180648804</v>
       </c>
       <c r="L11" t="n">
-        <v>4.82111554145813</v>
+        <v>4.854647135734558</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.18092155456543</v>
+        <v>3.828761100769043</v>
       </c>
       <c r="C12" t="n">
-        <v>3.970859050750732</v>
+        <v>3.81479811668396</v>
       </c>
       <c r="D12" t="n">
-        <v>4.239206552505493</v>
+        <v>3.923508167266846</v>
       </c>
       <c r="E12" t="n">
-        <v>3.814444303512573</v>
+        <v>3.941459655761719</v>
       </c>
       <c r="F12" t="n">
-        <v>4.30850887298584</v>
+        <v>4.438132047653198</v>
       </c>
       <c r="G12" t="n">
-        <v>3.967186212539673</v>
+        <v>4.343384504318237</v>
       </c>
       <c r="H12" t="n">
-        <v>4.397889375686646</v>
+        <v>4.380285978317261</v>
       </c>
       <c r="I12" t="n">
-        <v>4.215582609176636</v>
+        <v>4.154889583587646</v>
       </c>
       <c r="J12" t="n">
-        <v>3.905791044235229</v>
+        <v>4.026232481002808</v>
       </c>
       <c r="K12" t="n">
-        <v>4.160927772521973</v>
+        <v>4.193379402160645</v>
       </c>
       <c r="L12" t="n">
-        <v>4.116131734848023</v>
+        <v>4.104483103752136</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.593630313873291</v>
+        <v>4.540856599807739</v>
       </c>
       <c r="C13" t="n">
-        <v>5.183153629302979</v>
+        <v>4.755283117294312</v>
       </c>
       <c r="D13" t="n">
-        <v>4.559336185455322</v>
+        <v>4.747304439544678</v>
       </c>
       <c r="E13" t="n">
-        <v>5.357410907745361</v>
+        <v>4.704419851303101</v>
       </c>
       <c r="F13" t="n">
-        <v>5.139672756195068</v>
+        <v>4.525896549224854</v>
       </c>
       <c r="G13" t="n">
-        <v>4.91642427444458</v>
+        <v>4.406217336654663</v>
       </c>
       <c r="H13" t="n">
-        <v>4.682733774185181</v>
+        <v>4.631093978881836</v>
       </c>
       <c r="I13" t="n">
-        <v>4.626410245895386</v>
+        <v>4.890920639038086</v>
       </c>
       <c r="J13" t="n">
-        <v>4.818632125854492</v>
+        <v>4.303821086883545</v>
       </c>
       <c r="K13" t="n">
-        <v>5.111435890197754</v>
+        <v>4.225699424743652</v>
       </c>
       <c r="L13" t="n">
-        <v>4.898884010314942</v>
+        <v>4.573151302337647</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.879438400268555</v>
+        <v>3.851698637008667</v>
       </c>
       <c r="C14" t="n">
-        <v>4.626605272293091</v>
+        <v>4.177828073501587</v>
       </c>
       <c r="D14" t="n">
-        <v>4.624345064163208</v>
+        <v>3.907550811767578</v>
       </c>
       <c r="E14" t="n">
-        <v>4.526131153106689</v>
+        <v>4.358344793319702</v>
       </c>
       <c r="F14" t="n">
-        <v>4.794976711273193</v>
+        <v>3.931486129760742</v>
       </c>
       <c r="G14" t="n">
-        <v>4.644716262817383</v>
+        <v>4.719378709793091</v>
       </c>
       <c r="H14" t="n">
-        <v>4.451367139816284</v>
+        <v>4.681480884552002</v>
       </c>
       <c r="I14" t="n">
-        <v>4.297624588012695</v>
+        <v>4.003294467926025</v>
       </c>
       <c r="J14" t="n">
-        <v>4.179346561431885</v>
+        <v>4.383277893066406</v>
       </c>
       <c r="K14" t="n">
-        <v>4.334481954574585</v>
+        <v>4.149902582168579</v>
       </c>
       <c r="L14" t="n">
-        <v>4.535903310775756</v>
+        <v>4.216424298286438</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>5.030224323272705</v>
+        <v>4.652557611465454</v>
       </c>
       <c r="C15" t="n">
-        <v>4.39043402671814</v>
+        <v>4.405219793319702</v>
       </c>
       <c r="D15" t="n">
-        <v>4.399373054504395</v>
+        <v>4.640590667724609</v>
       </c>
       <c r="E15" t="n">
-        <v>5.046411037445068</v>
+        <v>4.808141231536865</v>
       </c>
       <c r="F15" t="n">
-        <v>4.487651586532593</v>
+        <v>4.619646072387695</v>
       </c>
       <c r="G15" t="n">
-        <v>5.330399036407471</v>
+        <v>4.980680704116821</v>
       </c>
       <c r="H15" t="n">
-        <v>4.991479396820068</v>
+        <v>4.427160978317261</v>
       </c>
       <c r="I15" t="n">
-        <v>5.889104127883911</v>
+        <v>4.146910190582275</v>
       </c>
       <c r="J15" t="n">
-        <v>4.494822978973389</v>
+        <v>4.75428581237793</v>
       </c>
       <c r="K15" t="n">
-        <v>5.309722661972046</v>
+        <v>4.858008146286011</v>
       </c>
       <c r="L15" t="n">
-        <v>4.936962223052978</v>
+        <v>4.629320120811462</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.279887199401855</v>
+        <v>3.80981183052063</v>
       </c>
       <c r="C16" t="n">
-        <v>4.148248672485352</v>
+        <v>3.967390298843384</v>
       </c>
       <c r="D16" t="n">
-        <v>3.984664678573608</v>
+        <v>3.869651794433594</v>
       </c>
       <c r="E16" t="n">
-        <v>4.019027948379517</v>
+        <v>4.119982957839966</v>
       </c>
       <c r="F16" t="n">
-        <v>7.464787244796753</v>
+        <v>3.976366519927979</v>
       </c>
       <c r="G16" t="n">
-        <v>6.996103286743164</v>
+        <v>3.959412574768066</v>
       </c>
       <c r="H16" t="n">
-        <v>4.202973604202271</v>
+        <v>4.351364135742188</v>
       </c>
       <c r="I16" t="n">
-        <v>4.673936367034912</v>
+        <v>4.151896476745605</v>
       </c>
       <c r="J16" t="n">
-        <v>5.464656114578247</v>
+        <v>4.00628662109375</v>
       </c>
       <c r="K16" t="n">
-        <v>4.269382238388062</v>
+        <v>4.152900457382202</v>
       </c>
       <c r="L16" t="n">
-        <v>4.950366735458374</v>
+        <v>4.036506366729737</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>5.146663427352905</v>
+        <v>3.90755033493042</v>
       </c>
       <c r="C17" t="n">
-        <v>5.182454109191895</v>
+        <v>4.306483507156372</v>
       </c>
       <c r="D17" t="n">
-        <v>5.591405630111694</v>
+        <v>4.117988348007202</v>
       </c>
       <c r="E17" t="n">
-        <v>5.544070959091187</v>
+        <v>4.296509742736816</v>
       </c>
       <c r="F17" t="n">
-        <v>4.602237939834595</v>
+        <v>4.187801122665405</v>
       </c>
       <c r="G17" t="n">
-        <v>5.565148830413818</v>
+        <v>4.261603355407715</v>
       </c>
       <c r="H17" t="n">
-        <v>5.204065799713135</v>
+        <v>4.152894735336304</v>
       </c>
       <c r="I17" t="n">
-        <v>4.427978038787842</v>
+        <v>3.983347415924072</v>
       </c>
       <c r="J17" t="n">
-        <v>5.302304983139038</v>
+        <v>4.180819749832153</v>
       </c>
       <c r="K17" t="n">
-        <v>5.110641002655029</v>
+        <v>4.157880544662476</v>
       </c>
       <c r="L17" t="n">
-        <v>5.167697072029114</v>
+        <v>4.155287885665894</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>5.685556650161743</v>
+        <v>4.101033449172974</v>
       </c>
       <c r="C18" t="n">
-        <v>5.395300149917603</v>
+        <v>4.186803579330444</v>
       </c>
       <c r="D18" t="n">
-        <v>4.375537157058716</v>
+        <v>4.137934684753418</v>
       </c>
       <c r="E18" t="n">
-        <v>5.45619535446167</v>
+        <v>4.633608818054199</v>
       </c>
       <c r="F18" t="n">
-        <v>4.586877822875977</v>
+        <v>4.735336065292358</v>
       </c>
       <c r="G18" t="n">
-        <v>4.638435840606689</v>
+        <v>4.093054294586182</v>
       </c>
       <c r="H18" t="n">
-        <v>5.230054140090942</v>
+        <v>4.57476544380188</v>
       </c>
       <c r="I18" t="n">
-        <v>5.123210191726685</v>
+        <v>4.175832986831665</v>
       </c>
       <c r="J18" t="n">
-        <v>4.491053104400635</v>
+        <v>4.192787170410156</v>
       </c>
       <c r="K18" t="n">
-        <v>4.225394248962402</v>
+        <v>4.344381809234619</v>
       </c>
       <c r="L18" t="n">
-        <v>4.920761466026306</v>
+        <v>4.31755383014679</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.759582757949829</v>
+        <v>4.051167011260986</v>
       </c>
       <c r="C19" t="n">
-        <v>4.436292409896851</v>
+        <v>3.851699829101562</v>
       </c>
       <c r="D19" t="n">
-        <v>4.624967813491821</v>
+        <v>3.891592502593994</v>
       </c>
       <c r="E19" t="n">
-        <v>5.308987855911255</v>
+        <v>4.479009628295898</v>
       </c>
       <c r="F19" t="n">
-        <v>5.369456052780151</v>
+        <v>4.387267827987671</v>
       </c>
       <c r="G19" t="n">
-        <v>4.821981430053711</v>
+        <v>4.459074735641479</v>
       </c>
       <c r="H19" t="n">
-        <v>4.093707084655762</v>
+        <v>3.953427314758301</v>
       </c>
       <c r="I19" t="n">
-        <v>4.552398204803467</v>
+        <v>3.913533926010132</v>
       </c>
       <c r="J19" t="n">
-        <v>4.288630962371826</v>
+        <v>3.939464569091797</v>
       </c>
       <c r="K19" t="n">
-        <v>4.622672557830811</v>
+        <v>4.013268232345581</v>
       </c>
       <c r="L19" t="n">
-        <v>4.687867712974549</v>
+        <v>4.09395055770874</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.563004016876221</v>
+        <v>5.334733963012695</v>
       </c>
       <c r="C20" t="n">
-        <v>5.364540100097656</v>
+        <v>4.739326238632202</v>
       </c>
       <c r="D20" t="n">
-        <v>5.569933891296387</v>
+        <v>4.591720342636108</v>
       </c>
       <c r="E20" t="n">
-        <v>4.888169527053833</v>
+        <v>4.534873723983765</v>
       </c>
       <c r="F20" t="n">
-        <v>5.333436012268066</v>
+        <v>4.580750226974487</v>
       </c>
       <c r="G20" t="n">
-        <v>5.008978366851807</v>
+        <v>4.8759605884552</v>
       </c>
       <c r="H20" t="n">
-        <v>5.056607246398926</v>
+        <v>5.344707012176514</v>
       </c>
       <c r="I20" t="n">
-        <v>5.271340131759644</v>
+        <v>5.145241260528564</v>
       </c>
       <c r="J20" t="n">
-        <v>5.535442352294922</v>
+        <v>4.753288745880127</v>
       </c>
       <c r="K20" t="n">
-        <v>5.771021127700806</v>
+        <v>5.24397611618042</v>
       </c>
       <c r="L20" t="n">
-        <v>5.236247277259826</v>
+        <v>4.914457821846009</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.879069566726685</v>
+        <v>4.405219554901123</v>
       </c>
       <c r="C21" t="n">
-        <v>4.654926061630249</v>
+        <v>4.214729309082031</v>
       </c>
       <c r="D21" t="n">
-        <v>4.873541116714478</v>
+        <v>3.886606454849243</v>
       </c>
       <c r="E21" t="n">
-        <v>5.683058261871338</v>
+        <v>4.331417083740234</v>
       </c>
       <c r="F21" t="n">
-        <v>4.239832878112793</v>
+        <v>3.93647289276123</v>
       </c>
       <c r="G21" t="n">
-        <v>4.338218927383423</v>
+        <v>4.208745241165161</v>
       </c>
       <c r="H21" t="n">
-        <v>5.224822282791138</v>
+        <v>4.434141635894775</v>
       </c>
       <c r="I21" t="n">
-        <v>4.805130243301392</v>
+        <v>4.81911301612854</v>
       </c>
       <c r="J21" t="n">
-        <v>4.570318698883057</v>
+        <v>3.8267662525177</v>
       </c>
       <c r="K21" t="n">
-        <v>4.478719711303711</v>
+        <v>4.013268232345581</v>
       </c>
       <c r="L21" t="n">
-        <v>4.774763774871826</v>
+        <v>4.207647967338562</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.933743238449097</v>
+        <v>4.286536693572998</v>
       </c>
       <c r="C22" t="n">
-        <v>5.015028715133667</v>
+        <v>4.190792560577393</v>
       </c>
       <c r="D22" t="n">
-        <v>4.549698114395142</v>
+        <v>4.31745433807373</v>
       </c>
       <c r="E22" t="n">
-        <v>4.493233919143677</v>
+        <v>4.246643781661987</v>
       </c>
       <c r="F22" t="n">
-        <v>4.66254186630249</v>
+        <v>4.712397813796997</v>
       </c>
       <c r="G22" t="n">
-        <v>4.565319538116455</v>
+        <v>4.595709562301636</v>
       </c>
       <c r="H22" t="n">
-        <v>4.717788457870483</v>
+        <v>4.249635457992554</v>
       </c>
       <c r="I22" t="n">
-        <v>4.466504096984863</v>
+        <v>5.385597705841064</v>
       </c>
       <c r="J22" t="n">
-        <v>5.015394926071167</v>
+        <v>4.273571014404297</v>
       </c>
       <c r="K22" t="n">
-        <v>4.192929267883301</v>
+        <v>4.71539044380188</v>
       </c>
       <c r="L22" t="n">
-        <v>4.661218214035034</v>
+        <v>4.497372937202454</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.527312755584717</v>
+        <v>4.411203861236572</v>
       </c>
       <c r="C23" t="n">
-        <v>3.977032661437988</v>
+        <v>4.306483507156372</v>
       </c>
       <c r="D23" t="n">
-        <v>4.10708212852478</v>
+        <v>4.137933731079102</v>
       </c>
       <c r="E23" t="n">
-        <v>4.402489900588989</v>
+        <v>4.331416606903076</v>
       </c>
       <c r="F23" t="n">
-        <v>4.043856859207153</v>
+        <v>4.12696361541748</v>
       </c>
       <c r="G23" t="n">
-        <v>4.202345132827759</v>
+        <v>4.443118095397949</v>
       </c>
       <c r="H23" t="n">
-        <v>4.602028608322144</v>
+        <v>3.825769186019897</v>
       </c>
       <c r="I23" t="n">
-        <v>4.503117799758911</v>
+        <v>4.32244086265564</v>
       </c>
       <c r="J23" t="n">
-        <v>4.459771156311035</v>
+        <v>4.174835443496704</v>
       </c>
       <c r="K23" t="n">
-        <v>4.17209267616272</v>
+        <v>4.092057943344116</v>
       </c>
       <c r="L23" t="n">
-        <v>4.29971296787262</v>
+        <v>4.217222285270691</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.850001811981201</v>
+        <v>4.570776462554932</v>
       </c>
       <c r="C24" t="n">
-        <v>4.742623090744019</v>
+        <v>5.17216968536377</v>
       </c>
       <c r="D24" t="n">
-        <v>4.656824827194214</v>
+        <v>5.340717315673828</v>
       </c>
       <c r="E24" t="n">
-        <v>4.438541412353516</v>
+        <v>5.030547618865967</v>
       </c>
       <c r="F24" t="n">
-        <v>4.880628108978271</v>
+        <v>5.053485870361328</v>
       </c>
       <c r="G24" t="n">
-        <v>4.766854047775269</v>
+        <v>4.243651390075684</v>
       </c>
       <c r="H24" t="n">
-        <v>4.589977979660034</v>
+        <v>4.615656614303589</v>
       </c>
       <c r="I24" t="n">
-        <v>4.770000219345093</v>
+        <v>4.514926195144653</v>
       </c>
       <c r="J24" t="n">
-        <v>4.819127798080444</v>
+        <v>4.474035263061523</v>
       </c>
       <c r="K24" t="n">
-        <v>4.865963697433472</v>
+        <v>4.684473276138306</v>
       </c>
       <c r="L24" t="n">
-        <v>4.738054299354554</v>
+        <v>4.770043969154358</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>5.243096828460693</v>
+        <v>4.163865566253662</v>
       </c>
       <c r="C25" t="n">
-        <v>4.181181192398071</v>
+        <v>4.555816411972046</v>
       </c>
       <c r="D25" t="n">
-        <v>4.156978607177734</v>
+        <v>4.299609661102295</v>
       </c>
       <c r="E25" t="n">
-        <v>4.515880584716797</v>
+        <v>4.950761318206787</v>
       </c>
       <c r="F25" t="n">
-        <v>4.422525405883789</v>
+        <v>4.837064027786255</v>
       </c>
       <c r="G25" t="n">
-        <v>4.877914667129517</v>
+        <v>4.587007999420166</v>
       </c>
       <c r="H25" t="n">
-        <v>4.907781600952148</v>
+        <v>4.348371028900146</v>
       </c>
       <c r="I25" t="n">
-        <v>5.771485567092896</v>
+        <v>4.495976209640503</v>
       </c>
       <c r="J25" t="n">
-        <v>4.320287227630615</v>
+        <v>4.412455081939697</v>
       </c>
       <c r="K25" t="n">
-        <v>4.10823392868042</v>
+        <v>4.75528359413147</v>
       </c>
       <c r="L25" t="n">
-        <v>4.650536561012268</v>
+        <v>4.540621089935303</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>5.173855066299438</v>
+        <v>5.979010820388794</v>
       </c>
       <c r="C26" t="n">
-        <v>4.233197689056396</v>
+        <v>5.009602785110474</v>
       </c>
       <c r="D26" t="n">
-        <v>4.582282781600952</v>
+        <v>4.962630271911621</v>
       </c>
       <c r="E26" t="n">
-        <v>4.689928531646729</v>
+        <v>4.868978500366211</v>
       </c>
       <c r="F26" t="n">
-        <v>4.234537601470947</v>
+        <v>6.040319681167603</v>
       </c>
       <c r="G26" t="n">
-        <v>5.015037298202515</v>
+        <v>4.678489446640015</v>
       </c>
       <c r="H26" t="n">
-        <v>5.074950218200684</v>
+        <v>5.224030017852783</v>
       </c>
       <c r="I26" t="n">
-        <v>4.426408290863037</v>
+        <v>5.030545949935913</v>
       </c>
       <c r="J26" t="n">
-        <v>4.258713960647583</v>
+        <v>4.88094687461853</v>
       </c>
       <c r="K26" t="n">
-        <v>4.786121845245361</v>
+        <v>4.324436187744141</v>
       </c>
       <c r="L26" t="n">
-        <v>4.647503328323364</v>
+        <v>5.099899053573608</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>3.952969789505005</v>
+        <v>4.96871280670166</v>
       </c>
       <c r="C27" t="n">
-        <v>3.849056005477905</v>
+        <v>4.442120790481567</v>
       </c>
       <c r="D27" t="n">
-        <v>3.805654525756836</v>
+        <v>3.94544792175293</v>
       </c>
       <c r="E27" t="n">
-        <v>4.356674432754517</v>
+        <v>4.593716144561768</v>
       </c>
       <c r="F27" t="n">
-        <v>4.430950164794922</v>
+        <v>4.758275032043457</v>
       </c>
       <c r="G27" t="n">
-        <v>4.151753664016724</v>
+        <v>4.169848680496216</v>
       </c>
       <c r="H27" t="n">
-        <v>4.186117172241211</v>
+        <v>3.937471389770508</v>
       </c>
       <c r="I27" t="n">
-        <v>3.745063543319702</v>
+        <v>4.769246101379395</v>
       </c>
       <c r="J27" t="n">
-        <v>4.376884937286377</v>
+        <v>4.363331079483032</v>
       </c>
       <c r="K27" t="n">
-        <v>4.633090257644653</v>
+        <v>4.342387676239014</v>
       </c>
       <c r="L27" t="n">
-        <v>4.148821449279785</v>
+        <v>4.429055762290955</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.473377227783203</v>
+        <v>4.10302734375</v>
       </c>
       <c r="C28" t="n">
-        <v>3.973330020904541</v>
+        <v>4.124969244003296</v>
       </c>
       <c r="D28" t="n">
-        <v>4.079328775405884</v>
+        <v>4.120979785919189</v>
       </c>
       <c r="E28" t="n">
-        <v>3.731947660446167</v>
+        <v>4.467054128646851</v>
       </c>
       <c r="F28" t="n">
-        <v>4.447263956069946</v>
+        <v>4.381283283233643</v>
       </c>
       <c r="G28" t="n">
-        <v>4.588078737258911</v>
+        <v>4.022243976593018</v>
       </c>
       <c r="H28" t="n">
-        <v>4.990968227386475</v>
+        <v>4.212734460830688</v>
       </c>
       <c r="I28" t="n">
-        <v>4.070704936981201</v>
+        <v>4.140926599502563</v>
       </c>
       <c r="J28" t="n">
-        <v>3.910643100738525</v>
+        <v>3.774905204772949</v>
       </c>
       <c r="K28" t="n">
-        <v>4.545322418212891</v>
+        <v>4.231683254241943</v>
       </c>
       <c r="L28" t="n">
-        <v>4.281096506118774</v>
+        <v>4.157980728149414</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>3.844498157501221</v>
+        <v>4.311469793319702</v>
       </c>
       <c r="C29" t="n">
-        <v>5.0229332447052</v>
+        <v>4.118984937667847</v>
       </c>
       <c r="D29" t="n">
-        <v>4.244846820831299</v>
+        <v>4.20276141166687</v>
       </c>
       <c r="E29" t="n">
-        <v>4.278913497924805</v>
+        <v>6.321322441101074</v>
       </c>
       <c r="F29" t="n">
-        <v>4.170717716217041</v>
+        <v>4.180819511413574</v>
       </c>
       <c r="G29" t="n">
-        <v>4.31247878074646</v>
+        <v>4.28154993057251</v>
       </c>
       <c r="H29" t="n">
-        <v>4.548031091690063</v>
+        <v>4.38028621673584</v>
       </c>
       <c r="I29" t="n">
-        <v>4.157132148742676</v>
+        <v>4.027230262756348</v>
       </c>
       <c r="J29" t="n">
-        <v>4.693501710891724</v>
+        <v>3.907550573348999</v>
       </c>
       <c r="K29" t="n">
-        <v>3.967891216278076</v>
+        <v>4.216723442077637</v>
       </c>
       <c r="L29" t="n">
-        <v>4.324094438552857</v>
+        <v>4.39486985206604</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.375368595123291</v>
+        <v>4.281550168991089</v>
       </c>
       <c r="C30" t="n">
-        <v>4.083939552307129</v>
+        <v>4.416189670562744</v>
       </c>
       <c r="D30" t="n">
-        <v>4.653836011886597</v>
+        <v>3.816792726516724</v>
       </c>
       <c r="E30" t="n">
-        <v>4.684672355651855</v>
+        <v>4.262601375579834</v>
       </c>
       <c r="F30" t="n">
-        <v>3.792612791061401</v>
+        <v>4.312467813491821</v>
       </c>
       <c r="G30" t="n">
-        <v>4.517078161239624</v>
+        <v>4.188798189163208</v>
       </c>
       <c r="H30" t="n">
-        <v>4.134648323059082</v>
+        <v>4.177828073501587</v>
       </c>
       <c r="I30" t="n">
-        <v>3.933225631713867</v>
+        <v>4.103028059005737</v>
       </c>
       <c r="J30" t="n">
-        <v>4.885394811630249</v>
+        <v>3.974371671676636</v>
       </c>
       <c r="K30" t="n">
-        <v>4.447575092315674</v>
+        <v>4.723368883132935</v>
       </c>
       <c r="L30" t="n">
-        <v>4.350835132598877</v>
+        <v>4.225699663162231</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>5.553818464279175</v>
+        <v>4.364328861236572</v>
       </c>
       <c r="C31" t="n">
-        <v>5.101169109344482</v>
+        <v>5.270905017852783</v>
       </c>
       <c r="D31" t="n">
-        <v>5.062583923339844</v>
+        <v>4.472040414810181</v>
       </c>
       <c r="E31" t="n">
-        <v>4.419830799102783</v>
+        <v>4.524899482727051</v>
       </c>
       <c r="F31" t="n">
-        <v>5.016885042190552</v>
+        <v>5.221037149429321</v>
       </c>
       <c r="G31" t="n">
-        <v>4.860271215438843</v>
+        <v>5.490317583084106</v>
       </c>
       <c r="H31" t="n">
-        <v>4.469853639602661</v>
+        <v>5.885262250900269</v>
       </c>
       <c r="I31" t="n">
-        <v>4.567430734634399</v>
+        <v>5.414519786834717</v>
       </c>
       <c r="J31" t="n">
-        <v>5.316087961196899</v>
+        <v>5.61398720741272</v>
       </c>
       <c r="K31" t="n">
-        <v>4.991111993789673</v>
+        <v>5.155214071273804</v>
       </c>
       <c r="L31" t="n">
-        <v>4.935904288291932</v>
+        <v>5.141251182556152</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>5.59328818321228</v>
+        <v>4.558807849884033</v>
       </c>
       <c r="C32" t="n">
-        <v>4.466084241867065</v>
+        <v>4.928819417953491</v>
       </c>
       <c r="D32" t="n">
-        <v>5.223468780517578</v>
+        <v>4.414196252822876</v>
       </c>
       <c r="E32" t="n">
-        <v>4.60551381111145</v>
+        <v>4.195779085159302</v>
       </c>
       <c r="F32" t="n">
-        <v>5.512015819549561</v>
+        <v>4.697437524795532</v>
       </c>
       <c r="G32" t="n">
-        <v>5.004106283187866</v>
+        <v>4.387268304824829</v>
       </c>
       <c r="H32" t="n">
-        <v>4.556163311004639</v>
+        <v>4.767250776290894</v>
       </c>
       <c r="I32" t="n">
-        <v>4.794975996017456</v>
+        <v>4.515923738479614</v>
       </c>
       <c r="J32" t="n">
-        <v>4.778999805450439</v>
+        <v>5.137261867523193</v>
       </c>
       <c r="K32" t="n">
-        <v>4.519440174102783</v>
+        <v>4.547837972640991</v>
       </c>
       <c r="L32" t="n">
-        <v>4.905405640602112</v>
+        <v>4.615058279037475</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>5.107045650482178</v>
+        <v>4.554819583892822</v>
       </c>
       <c r="C33" t="n">
-        <v>4.107882499694824</v>
+        <v>4.740323305130005</v>
       </c>
       <c r="D33" t="n">
-        <v>4.430493831634521</v>
+        <v>4.338397979736328</v>
       </c>
       <c r="E33" t="n">
-        <v>4.710108995437622</v>
+        <v>4.750296592712402</v>
       </c>
       <c r="F33" t="n">
-        <v>4.497673034667969</v>
+        <v>4.378292322158813</v>
       </c>
       <c r="G33" t="n">
-        <v>4.647493600845337</v>
+        <v>4.659539222717285</v>
       </c>
       <c r="H33" t="n">
-        <v>5.051819562911987</v>
+        <v>4.483011484146118</v>
       </c>
       <c r="I33" t="n">
-        <v>4.199414730072021</v>
+        <v>4.341390132904053</v>
       </c>
       <c r="J33" t="n">
-        <v>4.268320322036743</v>
+        <v>4.564793348312378</v>
       </c>
       <c r="K33" t="n">
-        <v>4.19257378578186</v>
+        <v>4.428158044815063</v>
       </c>
       <c r="L33" t="n">
-        <v>4.521282601356506</v>
+        <v>4.523902201652527</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>4.683101654052734</v>
+        <v>3.729027509689331</v>
       </c>
       <c r="C34" t="n">
-        <v>3.923113584518433</v>
+        <v>3.728217840194702</v>
       </c>
       <c r="D34" t="n">
-        <v>3.744370937347412</v>
+        <v>4.691054582595825</v>
       </c>
       <c r="E34" t="n">
-        <v>3.808029174804688</v>
+        <v>4.214729070663452</v>
       </c>
       <c r="F34" t="n">
-        <v>3.755100727081299</v>
+        <v>3.917523384094238</v>
       </c>
       <c r="G34" t="n">
-        <v>3.814444065093994</v>
+        <v>3.768920660018921</v>
       </c>
       <c r="H34" t="n">
-        <v>4.022879600524902</v>
+        <v>3.932484149932861</v>
       </c>
       <c r="I34" t="n">
-        <v>3.873334646224976</v>
+        <v>3.785875558853149</v>
       </c>
       <c r="J34" t="n">
-        <v>3.621785163879395</v>
+        <v>4.007284164428711</v>
       </c>
       <c r="K34" t="n">
-        <v>4.502394676208496</v>
+        <v>4.49597692489624</v>
       </c>
       <c r="L34" t="n">
-        <v>3.974855422973633</v>
+        <v>4.027109384536743</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.520728349685669</v>
+        <v>3.818787336349487</v>
       </c>
       <c r="C35" t="n">
-        <v>3.654169321060181</v>
+        <v>4.043187618255615</v>
       </c>
       <c r="D35" t="n">
-        <v>4.951165437698364</v>
+        <v>4.227694272994995</v>
       </c>
       <c r="E35" t="n">
-        <v>3.801209688186646</v>
+        <v>3.961406707763672</v>
       </c>
       <c r="F35" t="n">
-        <v>3.579483985900879</v>
+        <v>4.157880544662476</v>
       </c>
       <c r="G35" t="n">
-        <v>4.185108423233032</v>
+        <v>4.317453384399414</v>
       </c>
       <c r="H35" t="n">
-        <v>4.059868574142456</v>
+        <v>3.862670660018921</v>
       </c>
       <c r="I35" t="n">
-        <v>3.819883584976196</v>
+        <v>3.952460289001465</v>
       </c>
       <c r="J35" t="n">
-        <v>4.438522338867188</v>
+        <v>3.661192893981934</v>
       </c>
       <c r="K35" t="n">
-        <v>3.993528127670288</v>
+        <v>3.680158138275146</v>
       </c>
       <c r="L35" t="n">
-        <v>4.10036678314209</v>
+        <v>3.968289184570312</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>4.28101921081543</v>
+        <v>4.025235652923584</v>
       </c>
       <c r="C36" t="n">
-        <v>5.164355278015137</v>
+        <v>4.205753564834595</v>
       </c>
       <c r="D36" t="n">
-        <v>5.021502017974854</v>
+        <v>3.896579265594482</v>
       </c>
       <c r="E36" t="n">
-        <v>4.566817283630371</v>
+        <v>4.38627028465271</v>
       </c>
       <c r="F36" t="n">
-        <v>4.535544633865356</v>
+        <v>4.250633001327515</v>
       </c>
       <c r="G36" t="n">
-        <v>4.407798051834106</v>
+        <v>4.02922511100769</v>
       </c>
       <c r="H36" t="n">
-        <v>4.268803834915161</v>
+        <v>3.863667726516724</v>
       </c>
       <c r="I36" t="n">
-        <v>4.252493381500244</v>
+        <v>4.364329099655151</v>
       </c>
       <c r="J36" t="n">
-        <v>4.545974254608154</v>
+        <v>4.57576322555542</v>
       </c>
       <c r="K36" t="n">
-        <v>4.341923713684082</v>
+        <v>4.056153535842896</v>
       </c>
       <c r="L36" t="n">
-        <v>4.53862316608429</v>
+        <v>4.165361046791077</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.438571691513062</v>
+        <v>4.893913507461548</v>
       </c>
       <c r="C37" t="n">
-        <v>4.729609251022339</v>
+        <v>5.314786434173584</v>
       </c>
       <c r="D37" t="n">
-        <v>4.855362892150879</v>
+        <v>5.11232852935791</v>
       </c>
       <c r="E37" t="n">
-        <v>5.208719968795776</v>
+        <v>5.058472394943237</v>
       </c>
       <c r="F37" t="n">
-        <v>5.355252981185913</v>
+        <v>5.943106412887573</v>
       </c>
       <c r="G37" t="n">
-        <v>5.744130611419678</v>
+        <v>5.628947019577026</v>
       </c>
       <c r="H37" t="n">
-        <v>4.860237121582031</v>
+        <v>5.138258934020996</v>
       </c>
       <c r="I37" t="n">
-        <v>5.848607778549194</v>
+        <v>5.541182279586792</v>
       </c>
       <c r="J37" t="n">
-        <v>5.009969472885132</v>
+        <v>5.013593196868896</v>
       </c>
       <c r="K37" t="n">
-        <v>5.903974771499634</v>
+        <v>4.932808876037598</v>
       </c>
       <c r="L37" t="n">
-        <v>5.295443654060364</v>
+        <v>5.257739758491516</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>3.984550476074219</v>
+        <v>3.925502061843872</v>
       </c>
       <c r="C38" t="n">
-        <v>4.580741405487061</v>
+        <v>3.963335752487183</v>
       </c>
       <c r="D38" t="n">
-        <v>3.905798435211182</v>
+        <v>3.73600959777832</v>
       </c>
       <c r="E38" t="n">
-        <v>4.246601581573486</v>
+        <v>3.817790746688843</v>
       </c>
       <c r="F38" t="n">
-        <v>3.864239692687988</v>
+        <v>3.972376585006714</v>
       </c>
       <c r="G38" t="n">
-        <v>4.29977560043335</v>
+        <v>4.111006259918213</v>
       </c>
       <c r="H38" t="n">
-        <v>4.661707878112793</v>
+        <v>3.937469959259033</v>
       </c>
       <c r="I38" t="n">
-        <v>4.511389255523682</v>
+        <v>4.028228282928467</v>
       </c>
       <c r="J38" t="n">
-        <v>3.706031084060669</v>
+        <v>4.344381093978882</v>
       </c>
       <c r="K38" t="n">
-        <v>4.539194345474243</v>
+        <v>3.984126091003418</v>
       </c>
       <c r="L38" t="n">
-        <v>4.230002975463867</v>
+        <v>3.982022643089294</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>3.91330099105835</v>
+        <v>4.069118976593018</v>
       </c>
       <c r="C39" t="n">
-        <v>3.961528539657593</v>
+        <v>3.800835371017456</v>
       </c>
       <c r="D39" t="n">
-        <v>4.728066921234131</v>
+        <v>3.773907423019409</v>
       </c>
       <c r="E39" t="n">
-        <v>4.558007955551147</v>
+        <v>3.939465522766113</v>
       </c>
       <c r="F39" t="n">
-        <v>4.292035102844238</v>
+        <v>3.742990016937256</v>
       </c>
       <c r="G39" t="n">
-        <v>3.869197607040405</v>
+        <v>3.890594959259033</v>
       </c>
       <c r="H39" t="n">
-        <v>3.91679048538208</v>
+        <v>3.876632928848267</v>
       </c>
       <c r="I39" t="n">
-        <v>3.940090656280518</v>
+        <v>4.061140060424805</v>
       </c>
       <c r="J39" t="n">
-        <v>4.540050506591797</v>
+        <v>3.813801527023315</v>
       </c>
       <c r="K39" t="n">
-        <v>4.005229949951172</v>
+        <v>3.782883644104004</v>
       </c>
       <c r="L39" t="n">
-        <v>4.172429871559143</v>
+        <v>3.875137042999268</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.512264490127563</v>
+        <v>5.068445682525635</v>
       </c>
       <c r="C40" t="n">
-        <v>4.51699161529541</v>
+        <v>5.013592481613159</v>
       </c>
       <c r="D40" t="n">
-        <v>4.215056657791138</v>
+        <v>4.524899959564209</v>
       </c>
       <c r="E40" t="n">
-        <v>5.195335626602173</v>
+        <v>4.643582105636597</v>
       </c>
       <c r="F40" t="n">
-        <v>4.333820819854736</v>
+        <v>4.332414150238037</v>
       </c>
       <c r="G40" t="n">
-        <v>4.813472509384155</v>
+        <v>4.863992214202881</v>
       </c>
       <c r="H40" t="n">
-        <v>5.565930128097534</v>
+        <v>4.836068153381348</v>
       </c>
       <c r="I40" t="n">
-        <v>4.705521583557129</v>
+        <v>4.421175718307495</v>
       </c>
       <c r="J40" t="n">
-        <v>5.227526664733887</v>
+        <v>4.600696802139282</v>
       </c>
       <c r="K40" t="n">
-        <v>4.536045551300049</v>
+        <v>4.794180154800415</v>
       </c>
       <c r="L40" t="n">
-        <v>4.762196564674378</v>
+        <v>4.709904742240906</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.120101451873779</v>
+        <v>4.128957748413086</v>
       </c>
       <c r="C41" t="n">
-        <v>4.858403444290161</v>
+        <v>4.262601613998413</v>
       </c>
       <c r="D41" t="n">
-        <v>4.140591621398926</v>
+        <v>4.169848442077637</v>
       </c>
       <c r="E41" t="n">
-        <v>4.739686727523804</v>
+        <v>4.423171520233154</v>
       </c>
       <c r="F41" t="n">
-        <v>4.726356744766235</v>
+        <v>3.998307466506958</v>
       </c>
       <c r="G41" t="n">
-        <v>4.090146780014038</v>
+        <v>4.158878326416016</v>
       </c>
       <c r="H41" t="n">
-        <v>4.255337476730347</v>
+        <v>4.551826953887939</v>
       </c>
       <c r="I41" t="n">
-        <v>4.22484278678894</v>
+        <v>4.131950378417969</v>
       </c>
       <c r="J41" t="n">
-        <v>4.304047584533691</v>
+        <v>4.183811664581299</v>
       </c>
       <c r="K41" t="n">
-        <v>4.678121566772461</v>
+        <v>3.993321180343628</v>
       </c>
       <c r="L41" t="n">
-        <v>4.413763618469238</v>
+        <v>4.20026752948761</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>5.67852783203125</v>
+        <v>4.352360725402832</v>
       </c>
       <c r="C42" t="n">
-        <v>4.372617721557617</v>
+        <v>4.462067365646362</v>
       </c>
       <c r="D42" t="n">
-        <v>4.713278770446777</v>
+        <v>4.68746542930603</v>
       </c>
       <c r="E42" t="n">
-        <v>4.861656188964844</v>
+        <v>4.539859533309937</v>
       </c>
       <c r="F42" t="n">
-        <v>4.769530773162842</v>
+        <v>4.427160263061523</v>
       </c>
       <c r="G42" t="n">
-        <v>4.845877408981323</v>
+        <v>4.653554916381836</v>
       </c>
       <c r="H42" t="n">
-        <v>4.597090482711792</v>
+        <v>4.363332271575928</v>
       </c>
       <c r="I42" t="n">
-        <v>4.863521814346313</v>
+        <v>4.652558326721191</v>
       </c>
       <c r="J42" t="n">
-        <v>5.013501167297363</v>
+        <v>4.751293897628784</v>
       </c>
       <c r="K42" t="n">
-        <v>4.992944478988647</v>
+        <v>4.560802698135376</v>
       </c>
       <c r="L42" t="n">
-        <v>4.870854663848877</v>
+        <v>4.54504554271698</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.238353252410889</v>
+        <v>4.480019569396973</v>
       </c>
       <c r="C43" t="n">
-        <v>4.358676671981812</v>
+        <v>4.312468290328979</v>
       </c>
       <c r="D43" t="n">
-        <v>4.183698892593384</v>
+        <v>4.3792884349823</v>
       </c>
       <c r="E43" t="n">
-        <v>4.838020086288452</v>
+        <v>4.577757835388184</v>
       </c>
       <c r="F43" t="n">
-        <v>5.14913535118103</v>
+        <v>4.23068642616272</v>
       </c>
       <c r="G43" t="n">
-        <v>5.313971996307373</v>
+        <v>5.14723539352417</v>
       </c>
       <c r="H43" t="n">
-        <v>4.22269344329834</v>
+        <v>4.309475660324097</v>
       </c>
       <c r="I43" t="n">
-        <v>4.176603317260742</v>
+        <v>4.438131332397461</v>
       </c>
       <c r="J43" t="n">
-        <v>4.733545064926147</v>
+        <v>4.184808969497681</v>
       </c>
       <c r="K43" t="n">
-        <v>4.751139879226685</v>
+        <v>4.440126419067383</v>
       </c>
       <c r="L43" t="n">
-        <v>4.596583795547486</v>
+        <v>4.449999833106995</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.81244421005249</v>
+        <v>4.039198875427246</v>
       </c>
       <c r="C44" t="n">
-        <v>4.266351938247681</v>
+        <v>4.150899887084961</v>
       </c>
       <c r="D44" t="n">
-        <v>4.750858545303345</v>
+        <v>4.038201093673706</v>
       </c>
       <c r="E44" t="n">
-        <v>4.643233299255371</v>
+        <v>4.46007251739502</v>
       </c>
       <c r="F44" t="n">
-        <v>5.162261962890625</v>
+        <v>4.68012523651123</v>
       </c>
       <c r="G44" t="n">
-        <v>5.415309906005859</v>
+        <v>5.036532163619995</v>
       </c>
       <c r="H44" t="n">
-        <v>4.810915470123291</v>
+        <v>4.046179294586182</v>
       </c>
       <c r="I44" t="n">
-        <v>4.403575897216797</v>
+        <v>4.02822732925415</v>
       </c>
       <c r="J44" t="n">
-        <v>4.977518796920776</v>
+        <v>4.093053817749023</v>
       </c>
       <c r="K44" t="n">
-        <v>4.36793041229248</v>
+        <v>3.967391014099121</v>
       </c>
       <c r="L44" t="n">
-        <v>4.761040043830872</v>
+        <v>4.253988122940063</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.537444114685059</v>
+        <v>4.228691577911377</v>
       </c>
       <c r="C45" t="n">
-        <v>4.027072668075562</v>
+        <v>4.333412170410156</v>
       </c>
       <c r="D45" t="n">
-        <v>4.194698095321655</v>
+        <v>3.813800573348999</v>
       </c>
       <c r="E45" t="n">
-        <v>4.238900184631348</v>
+        <v>4.184808731079102</v>
       </c>
       <c r="F45" t="n">
-        <v>4.316502094268799</v>
+        <v>4.170846223831177</v>
       </c>
       <c r="G45" t="n">
-        <v>3.990631103515625</v>
+        <v>4.389261722564697</v>
       </c>
       <c r="H45" t="n">
-        <v>4.072242021560669</v>
+        <v>4.049171686172485</v>
       </c>
       <c r="I45" t="n">
-        <v>4.465683221817017</v>
+        <v>3.906553030014038</v>
       </c>
       <c r="J45" t="n">
-        <v>3.932813405990601</v>
+        <v>4.077896595001221</v>
       </c>
       <c r="K45" t="n">
-        <v>4.304185152053833</v>
+        <v>4.256255626678467</v>
       </c>
       <c r="L45" t="n">
-        <v>4.208017206192016</v>
+        <v>4.141069793701172</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.077497005462646</v>
+        <v>4.864990234375</v>
       </c>
       <c r="C46" t="n">
-        <v>4.74331521987915</v>
+        <v>4.366323709487915</v>
       </c>
       <c r="D46" t="n">
-        <v>4.205551862716675</v>
+        <v>4.076099872589111</v>
       </c>
       <c r="E46" t="n">
-        <v>4.05298113822937</v>
+        <v>4.061139822006226</v>
       </c>
       <c r="F46" t="n">
-        <v>4.451020956039429</v>
+        <v>4.18779993057251</v>
       </c>
       <c r="G46" t="n">
-        <v>4.844595670700073</v>
+        <v>4.284542798995972</v>
       </c>
       <c r="H46" t="n">
-        <v>4.351883888244629</v>
+        <v>4.024238109588623</v>
       </c>
       <c r="I46" t="n">
-        <v>4.212665557861328</v>
+        <v>5.047510385513306</v>
       </c>
       <c r="J46" t="n">
-        <v>4.328134536743164</v>
+        <v>4.643582105636597</v>
       </c>
       <c r="K46" t="n">
-        <v>4.087834596633911</v>
+        <v>4.159789323806763</v>
       </c>
       <c r="L46" t="n">
-        <v>4.335548043251038</v>
+        <v>4.371601629257202</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.386688709259033</v>
+        <v>3.823773860931396</v>
       </c>
       <c r="C47" t="n">
-        <v>4.254497051239014</v>
+        <v>4.752291202545166</v>
       </c>
       <c r="D47" t="n">
-        <v>3.733409643173218</v>
+        <v>4.061139822006226</v>
       </c>
       <c r="E47" t="n">
-        <v>4.700261354446411</v>
+        <v>3.719054698944092</v>
       </c>
       <c r="F47" t="n">
-        <v>3.748195648193359</v>
+        <v>3.905555486679077</v>
       </c>
       <c r="G47" t="n">
-        <v>4.332408666610718</v>
+        <v>3.669187545776367</v>
       </c>
       <c r="H47" t="n">
-        <v>3.758656024932861</v>
+        <v>3.701103210449219</v>
       </c>
       <c r="I47" t="n">
-        <v>4.599877834320068</v>
+        <v>4.275946617126465</v>
       </c>
       <c r="J47" t="n">
-        <v>4.690563917160034</v>
+        <v>3.81978440284729</v>
       </c>
       <c r="K47" t="n">
-        <v>3.99859881401062</v>
+        <v>4.4261634349823</v>
       </c>
       <c r="L47" t="n">
-        <v>4.220315766334534</v>
+        <v>4.015400028228759</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.850237846374512</v>
+        <v>5.487325668334961</v>
       </c>
       <c r="C48" t="n">
-        <v>4.713102579116821</v>
+        <v>5.357879638671875</v>
       </c>
       <c r="D48" t="n">
-        <v>4.618481636047363</v>
+        <v>4.834073305130005</v>
       </c>
       <c r="E48" t="n">
-        <v>5.146482706069946</v>
+        <v>5.065633773803711</v>
       </c>
       <c r="F48" t="n">
-        <v>4.937058210372925</v>
+        <v>5.045018672943115</v>
       </c>
       <c r="G48" t="n">
-        <v>4.800002813339233</v>
+        <v>4.701427459716797</v>
       </c>
       <c r="H48" t="n">
-        <v>4.491360902786255</v>
+        <v>5.450424194335938</v>
       </c>
       <c r="I48" t="n">
-        <v>5.60071325302124</v>
+        <v>4.640589952468872</v>
       </c>
       <c r="J48" t="n">
-        <v>4.968459606170654</v>
+        <v>4.347250938415527</v>
       </c>
       <c r="K48" t="n">
-        <v>5.113489389419556</v>
+        <v>4.379289627075195</v>
       </c>
       <c r="L48" t="n">
-        <v>4.923938894271851</v>
+        <v>4.930891323089599</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>5.283352851867676</v>
+        <v>4.169559240341187</v>
       </c>
       <c r="C49" t="n">
-        <v>4.559195756912231</v>
+        <v>5.839384317398071</v>
       </c>
       <c r="D49" t="n">
-        <v>4.645376205444336</v>
+        <v>4.653555154800415</v>
       </c>
       <c r="E49" t="n">
-        <v>4.062020301818848</v>
+        <v>4.722167730331421</v>
       </c>
       <c r="F49" t="n">
-        <v>4.518507242202759</v>
+        <v>4.736334800720215</v>
       </c>
       <c r="G49" t="n">
-        <v>4.671533823013306</v>
+        <v>4.503955364227295</v>
       </c>
       <c r="H49" t="n">
-        <v>4.729134559631348</v>
+        <v>4.947769641876221</v>
       </c>
       <c r="I49" t="n">
-        <v>4.439517498016357</v>
+        <v>4.83606743812561</v>
       </c>
       <c r="J49" t="n">
-        <v>4.908931255340576</v>
+        <v>4.493863582611084</v>
       </c>
       <c r="K49" t="n">
-        <v>4.699698686599731</v>
+        <v>4.759272813796997</v>
       </c>
       <c r="L49" t="n">
-        <v>4.651726818084716</v>
+        <v>4.766193008422851</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.764374256134033</v>
+        <v>3.845715761184692</v>
       </c>
       <c r="C50" t="n">
-        <v>3.726315259933472</v>
+        <v>3.761919975280762</v>
       </c>
       <c r="D50" t="n">
-        <v>3.643796920776367</v>
+        <v>3.606356143951416</v>
       </c>
       <c r="E50" t="n">
-        <v>3.796729564666748</v>
+        <v>6.183733940124512</v>
       </c>
       <c r="F50" t="n">
-        <v>4.092699289321899</v>
+        <v>5.159508466720581</v>
       </c>
       <c r="G50" t="n">
-        <v>3.751834869384766</v>
+        <v>4.121646881103516</v>
       </c>
       <c r="H50" t="n">
-        <v>4.863808155059814</v>
+        <v>4.007493495941162</v>
       </c>
       <c r="I50" t="n">
-        <v>3.694852352142334</v>
+        <v>4.640519618988037</v>
       </c>
       <c r="J50" t="n">
-        <v>4.447941780090332</v>
+        <v>4.915622472763062</v>
       </c>
       <c r="K50" t="n">
-        <v>4.026458978652954</v>
+        <v>6.124886512756348</v>
       </c>
       <c r="L50" t="n">
-        <v>3.980881142616272</v>
+        <v>4.636740326881409</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.209042310714722</v>
+        <v>6.524460792541504</v>
       </c>
       <c r="C51" t="n">
-        <v>4.876811742782593</v>
+        <v>4.614687204360962</v>
       </c>
       <c r="D51" t="n">
-        <v>4.977536916732788</v>
+        <v>4.500650644302368</v>
       </c>
       <c r="E51" t="n">
-        <v>4.116569519042969</v>
+        <v>5.276301860809326</v>
       </c>
       <c r="F51" t="n">
-        <v>4.361334562301636</v>
+        <v>4.199325799942017</v>
       </c>
       <c r="G51" t="n">
-        <v>4.586582899093628</v>
+        <v>5.333549022674561</v>
       </c>
       <c r="H51" t="n">
-        <v>4.878230094909668</v>
+        <v>5.104820966720581</v>
       </c>
       <c r="I51" t="n">
-        <v>4.230131864547729</v>
+        <v>5.916007995605469</v>
       </c>
       <c r="J51" t="n">
-        <v>4.170974493026733</v>
+        <v>5.290213823318481</v>
       </c>
       <c r="K51" t="n">
-        <v>4.224320650100708</v>
+        <v>4.40981125831604</v>
       </c>
       <c r="L51" t="n">
-        <v>4.463153505325318</v>
+        <v>5.116982936859131</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.64556770324707</v>
+        <v>4.409699869155884</v>
       </c>
       <c r="C52" t="n">
-        <v>4.491289401054383</v>
+        <v>4.425084323883056</v>
       </c>
       <c r="D52" t="n">
-        <v>4.455101647377014</v>
+        <v>4.316199345588684</v>
       </c>
       <c r="E52" t="n">
-        <v>4.550453443527221</v>
+        <v>4.539651770591735</v>
       </c>
       <c r="F52" t="n">
-        <v>4.554927515983581</v>
+        <v>4.477508087158203</v>
       </c>
       <c r="G52" t="n">
-        <v>4.646098136901855</v>
+        <v>4.433603453636169</v>
       </c>
       <c r="H52" t="n">
-        <v>4.523817791938781</v>
+        <v>4.377736330032349</v>
       </c>
       <c r="I52" t="n">
-        <v>4.513383502960205</v>
+        <v>4.473540306091309</v>
       </c>
       <c r="J52" t="n">
-        <v>4.619835586547851</v>
+        <v>4.344973320960999</v>
       </c>
       <c r="K52" t="n">
-        <v>4.581043314933777</v>
+        <v>4.3833740234375</v>
       </c>
       <c r="L52" t="n">
-        <v>4.558151804447174</v>
+        <v>4.418137083053589</v>
       </c>
     </row>
   </sheetData>
